--- a/jenkintown.xlsx
+++ b/jenkintown.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB09C6CF-4443-40D9-8862-4748CCCAEE9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{23CF9E5B-85B5-4B8F-8BCC-A4DA4C2D7488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2014,7 +2014,7 @@
       <c r="G3" t="s">
         <v>8</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>19046</v>
       </c>
       <c r="I3" s="1" t="s">
@@ -2043,7 +2043,7 @@
       <c r="G4" t="s">
         <v>8</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>19046</v>
       </c>
       <c r="I4" s="1" t="s">
@@ -2072,7 +2072,7 @@
       <c r="G5" t="s">
         <v>8</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>19046</v>
       </c>
       <c r="I5" s="1" t="s">
@@ -2101,7 +2101,7 @@
       <c r="G6" t="s">
         <v>8</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>19046</v>
       </c>
       <c r="I6" s="1" t="s">
@@ -2130,7 +2130,7 @@
       <c r="G7" t="s">
         <v>8</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>19046</v>
       </c>
       <c r="I7" s="1" t="s">
@@ -2159,7 +2159,7 @@
       <c r="G8" t="s">
         <v>8</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>19046</v>
       </c>
       <c r="I8" s="1" t="s">
@@ -2188,7 +2188,7 @@
       <c r="G9" t="s">
         <v>8</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>19046</v>
       </c>
       <c r="I9" s="1" t="s">
@@ -2217,7 +2217,7 @@
       <c r="G10" t="s">
         <v>8</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>19046</v>
       </c>
       <c r="I10" s="1" t="s">
@@ -2246,7 +2246,7 @@
       <c r="G11" t="s">
         <v>8</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>19046</v>
       </c>
       <c r="I11" s="1" t="s">
@@ -2275,7 +2275,7 @@
       <c r="G12" t="s">
         <v>8</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>19046</v>
       </c>
       <c r="I12" s="1" t="s">
@@ -2304,7 +2304,7 @@
       <c r="G13" t="s">
         <v>8</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
         <v>19046</v>
       </c>
       <c r="I13" s="1" t="s">
@@ -2333,7 +2333,7 @@
       <c r="G14" t="s">
         <v>8</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="1">
         <v>19046</v>
       </c>
       <c r="I14" s="1" t="s">
@@ -2362,7 +2362,7 @@
       <c r="G15" t="s">
         <v>8</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
         <v>19046</v>
       </c>
       <c r="I15" s="1" t="s">
@@ -2391,7 +2391,7 @@
       <c r="G16" t="s">
         <v>55</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="1">
         <v>19046</v>
       </c>
       <c r="I16" s="1" t="s">
@@ -2420,7 +2420,7 @@
       <c r="G17" t="s">
         <v>57</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="1">
         <v>19046</v>
       </c>
       <c r="I17" s="1" t="s">
@@ -2449,7 +2449,7 @@
       <c r="G18" t="s">
         <v>8</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="1">
         <v>19046</v>
       </c>
       <c r="I18" s="1" t="s">
@@ -2478,7 +2478,7 @@
       <c r="G19" t="s">
         <v>8</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="1">
         <v>19046</v>
       </c>
       <c r="I19" s="1" t="s">
@@ -2507,7 +2507,7 @@
       <c r="G20" t="s">
         <v>8</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="1">
         <v>19046</v>
       </c>
       <c r="I20" s="1" t="s">
@@ -2536,7 +2536,7 @@
       <c r="G21" t="s">
         <v>8</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="1">
         <v>19046</v>
       </c>
       <c r="I21" s="1" t="s">
@@ -2565,7 +2565,7 @@
       <c r="G22" t="s">
         <v>8</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="1">
         <v>19046</v>
       </c>
       <c r="I22" s="1" t="s">
@@ -2594,7 +2594,7 @@
       <c r="G23" t="s">
         <v>8</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="1">
         <v>19046</v>
       </c>
       <c r="I23" s="1" t="s">
@@ -2623,7 +2623,7 @@
       <c r="G24" t="s">
         <v>8</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="1">
         <v>19046</v>
       </c>
       <c r="I24" s="1" t="s">
@@ -2652,7 +2652,7 @@
       <c r="G25" t="s">
         <v>8</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="1">
         <v>19046</v>
       </c>
       <c r="I25" s="1" t="s">
@@ -2681,7 +2681,7 @@
       <c r="G26" t="s">
         <v>8</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="1">
         <v>19046</v>
       </c>
       <c r="I26" s="1" t="s">
@@ -2710,7 +2710,7 @@
       <c r="G27" t="s">
         <v>8</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="1">
         <v>19046</v>
       </c>
       <c r="I27" s="1" t="s">
@@ -2739,7 +2739,7 @@
       <c r="G28" t="s">
         <v>8</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="1">
         <v>19046</v>
       </c>
       <c r="I28" s="1" t="s">
@@ -2768,7 +2768,7 @@
       <c r="G29" t="s">
         <v>8</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="1">
         <v>19046</v>
       </c>
       <c r="I29" s="1" t="s">
@@ -2797,7 +2797,7 @@
       <c r="G30" t="s">
         <v>8</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="1">
         <v>19046</v>
       </c>
       <c r="I30" s="1" t="s">
@@ -2826,7 +2826,7 @@
       <c r="G31" t="s">
         <v>8</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="1">
         <v>19046</v>
       </c>
       <c r="I31" s="1" t="s">
@@ -2855,7 +2855,7 @@
       <c r="G32" t="s">
         <v>8</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="1">
         <v>19046</v>
       </c>
       <c r="I32" s="1" t="s">
@@ -2884,7 +2884,7 @@
       <c r="G33" t="s">
         <v>8</v>
       </c>
-      <c r="H33">
+      <c r="H33" s="1">
         <v>19046</v>
       </c>
       <c r="I33" s="1" t="s">
@@ -2913,7 +2913,7 @@
       <c r="G34" t="s">
         <v>8</v>
       </c>
-      <c r="H34">
+      <c r="H34" s="1">
         <v>19046</v>
       </c>
       <c r="I34" s="1" t="s">
@@ -2942,7 +2942,7 @@
       <c r="G35" t="s">
         <v>8</v>
       </c>
-      <c r="H35">
+      <c r="H35" s="1">
         <v>19046</v>
       </c>
       <c r="I35" s="1" t="s">
@@ -2971,7 +2971,7 @@
       <c r="G36" t="s">
         <v>8</v>
       </c>
-      <c r="H36">
+      <c r="H36" s="1">
         <v>19046</v>
       </c>
       <c r="I36" s="1" t="s">
@@ -3000,7 +3000,7 @@
       <c r="G37" t="s">
         <v>8</v>
       </c>
-      <c r="H37">
+      <c r="H37" s="1">
         <v>19046</v>
       </c>
       <c r="I37" s="1" t="s">
@@ -3029,7 +3029,7 @@
       <c r="G38" t="s">
         <v>8</v>
       </c>
-      <c r="H38">
+      <c r="H38" s="1">
         <v>19046</v>
       </c>
       <c r="I38" s="1" t="s">
@@ -3058,7 +3058,7 @@
       <c r="G39" t="s">
         <v>8</v>
       </c>
-      <c r="H39">
+      <c r="H39" s="1">
         <v>19046</v>
       </c>
       <c r="I39" s="1" t="s">
@@ -3087,7 +3087,7 @@
       <c r="G40" t="s">
         <v>8</v>
       </c>
-      <c r="H40">
+      <c r="H40" s="1">
         <v>19046</v>
       </c>
       <c r="I40" s="1" t="s">
@@ -3116,7 +3116,7 @@
       <c r="G41" t="s">
         <v>8</v>
       </c>
-      <c r="H41">
+      <c r="H41" s="1">
         <v>19046</v>
       </c>
       <c r="I41" s="1" t="s">
@@ -3145,7 +3145,7 @@
       <c r="G42" t="s">
         <v>8</v>
       </c>
-      <c r="H42">
+      <c r="H42" s="1">
         <v>19046</v>
       </c>
       <c r="I42" s="1" t="s">
@@ -3174,7 +3174,7 @@
       <c r="G43" t="s">
         <v>8</v>
       </c>
-      <c r="H43">
+      <c r="H43" s="1">
         <v>19046</v>
       </c>
       <c r="I43" s="1" t="s">
@@ -3203,7 +3203,7 @@
       <c r="G44" t="s">
         <v>8</v>
       </c>
-      <c r="H44">
+      <c r="H44" s="1">
         <v>19046</v>
       </c>
       <c r="I44" s="1" t="s">
@@ -3232,7 +3232,7 @@
       <c r="G45" t="s">
         <v>8</v>
       </c>
-      <c r="H45">
+      <c r="H45" s="1">
         <v>19046</v>
       </c>
       <c r="I45" s="1" t="s">
@@ -3261,7 +3261,7 @@
       <c r="G46" t="s">
         <v>8</v>
       </c>
-      <c r="H46">
+      <c r="H46" s="1">
         <v>19046</v>
       </c>
       <c r="I46" s="1" t="s">
@@ -3290,7 +3290,7 @@
       <c r="G47" t="s">
         <v>8</v>
       </c>
-      <c r="H47">
+      <c r="H47" s="1">
         <v>19046</v>
       </c>
       <c r="I47" s="1" t="s">
@@ -3319,7 +3319,7 @@
       <c r="G48" t="s">
         <v>8</v>
       </c>
-      <c r="H48">
+      <c r="H48" s="1">
         <v>19046</v>
       </c>
       <c r="I48" s="1" t="s">
@@ -3348,7 +3348,7 @@
       <c r="G49" t="s">
         <v>8</v>
       </c>
-      <c r="H49">
+      <c r="H49" s="1">
         <v>19046</v>
       </c>
       <c r="I49" s="1" t="s">
@@ -3377,7 +3377,7 @@
       <c r="G50" t="s">
         <v>8</v>
       </c>
-      <c r="H50">
+      <c r="H50" s="1">
         <v>19046</v>
       </c>
       <c r="I50" s="1" t="s">
@@ -3406,7 +3406,7 @@
       <c r="G51" t="s">
         <v>8</v>
       </c>
-      <c r="H51">
+      <c r="H51" s="1">
         <v>19046</v>
       </c>
       <c r="I51" s="1" t="s">
@@ -3435,7 +3435,7 @@
       <c r="G52" t="s">
         <v>8</v>
       </c>
-      <c r="H52">
+      <c r="H52" s="1">
         <v>19046</v>
       </c>
       <c r="I52" s="1" t="s">
@@ -3464,7 +3464,7 @@
       <c r="G53" t="s">
         <v>8</v>
       </c>
-      <c r="H53">
+      <c r="H53" s="1">
         <v>19046</v>
       </c>
       <c r="I53" s="1" t="s">
@@ -3493,7 +3493,7 @@
       <c r="G54" t="s">
         <v>8</v>
       </c>
-      <c r="H54">
+      <c r="H54" s="1">
         <v>19046</v>
       </c>
       <c r="I54" s="1" t="s">
@@ -3522,7 +3522,7 @@
       <c r="G55" t="s">
         <v>8</v>
       </c>
-      <c r="H55">
+      <c r="H55" s="1">
         <v>19046</v>
       </c>
       <c r="I55" s="1" t="s">
@@ -3551,7 +3551,7 @@
       <c r="G56" t="s">
         <v>8</v>
       </c>
-      <c r="H56">
+      <c r="H56" s="1">
         <v>19046</v>
       </c>
       <c r="I56" s="1" t="s">
@@ -3580,7 +3580,7 @@
       <c r="G57" t="s">
         <v>8</v>
       </c>
-      <c r="H57">
+      <c r="H57" s="1">
         <v>19046</v>
       </c>
       <c r="I57" s="1" t="s">
@@ -3609,7 +3609,7 @@
       <c r="G58" t="s">
         <v>8</v>
       </c>
-      <c r="H58">
+      <c r="H58" s="1">
         <v>19046</v>
       </c>
       <c r="I58" s="1" t="s">
@@ -3638,7 +3638,7 @@
       <c r="G59" t="s">
         <v>8</v>
       </c>
-      <c r="H59">
+      <c r="H59" s="1">
         <v>19046</v>
       </c>
       <c r="I59" s="1" t="s">
@@ -3667,7 +3667,7 @@
       <c r="G60" t="s">
         <v>8</v>
       </c>
-      <c r="H60">
+      <c r="H60" s="1">
         <v>19046</v>
       </c>
       <c r="I60" s="1" t="s">
@@ -3696,7 +3696,7 @@
       <c r="G61" t="s">
         <v>8</v>
       </c>
-      <c r="H61">
+      <c r="H61" s="1">
         <v>19046</v>
       </c>
       <c r="I61" s="1" t="s">
@@ -3725,7 +3725,7 @@
       <c r="G62" t="s">
         <v>8</v>
       </c>
-      <c r="H62">
+      <c r="H62" s="1">
         <v>19046</v>
       </c>
       <c r="I62" s="1" t="s">
@@ -3754,7 +3754,7 @@
       <c r="G63" t="s">
         <v>8</v>
       </c>
-      <c r="H63">
+      <c r="H63" s="1">
         <v>19046</v>
       </c>
       <c r="I63" s="1" t="s">
@@ -3783,7 +3783,7 @@
       <c r="G64" t="s">
         <v>8</v>
       </c>
-      <c r="H64">
+      <c r="H64" s="1">
         <v>19046</v>
       </c>
       <c r="I64" s="1" t="s">
@@ -3812,7 +3812,7 @@
       <c r="G65" t="s">
         <v>8</v>
       </c>
-      <c r="H65">
+      <c r="H65" s="1">
         <v>19046</v>
       </c>
       <c r="I65" s="1" t="s">
@@ -3841,7 +3841,7 @@
       <c r="G66" t="s">
         <v>8</v>
       </c>
-      <c r="H66">
+      <c r="H66" s="1">
         <v>19046</v>
       </c>
       <c r="I66" s="1" t="s">
@@ -3870,7 +3870,7 @@
       <c r="G67" t="s">
         <v>8</v>
       </c>
-      <c r="H67">
+      <c r="H67" s="1">
         <v>19046</v>
       </c>
       <c r="I67" s="1" t="s">
@@ -3899,7 +3899,7 @@
       <c r="G68" t="s">
         <v>8</v>
       </c>
-      <c r="H68">
+      <c r="H68" s="1">
         <v>19046</v>
       </c>
       <c r="I68" s="1" t="s">
@@ -3928,7 +3928,7 @@
       <c r="G69" t="s">
         <v>8</v>
       </c>
-      <c r="H69">
+      <c r="H69" s="1">
         <v>19046</v>
       </c>
       <c r="I69" s="1" t="s">
@@ -3957,7 +3957,7 @@
       <c r="G70" t="s">
         <v>8</v>
       </c>
-      <c r="H70">
+      <c r="H70" s="1">
         <v>19046</v>
       </c>
       <c r="I70" s="1" t="s">
@@ -3986,7 +3986,7 @@
       <c r="G71" t="s">
         <v>8</v>
       </c>
-      <c r="H71">
+      <c r="H71" s="1">
         <v>19046</v>
       </c>
       <c r="I71" s="1" t="s">
@@ -4015,7 +4015,7 @@
       <c r="G72" t="s">
         <v>8</v>
       </c>
-      <c r="H72">
+      <c r="H72" s="1">
         <v>19046</v>
       </c>
       <c r="I72" s="1" t="s">
@@ -4044,7 +4044,7 @@
       <c r="G73" t="s">
         <v>8</v>
       </c>
-      <c r="H73">
+      <c r="H73" s="1">
         <v>19046</v>
       </c>
       <c r="I73" s="1" t="s">
@@ -4073,7 +4073,7 @@
       <c r="G74" t="s">
         <v>8</v>
       </c>
-      <c r="H74">
+      <c r="H74" s="1">
         <v>19046</v>
       </c>
       <c r="I74" s="1" t="s">
@@ -4102,7 +4102,7 @@
       <c r="G75" t="s">
         <v>8</v>
       </c>
-      <c r="H75">
+      <c r="H75" s="1">
         <v>19046</v>
       </c>
       <c r="I75" s="1" t="s">
@@ -4131,7 +4131,7 @@
       <c r="G76" t="s">
         <v>8</v>
       </c>
-      <c r="H76">
+      <c r="H76" s="1">
         <v>19046</v>
       </c>
       <c r="I76" s="1" t="s">
@@ -4160,7 +4160,7 @@
       <c r="G77" t="s">
         <v>8</v>
       </c>
-      <c r="H77">
+      <c r="H77" s="1">
         <v>19046</v>
       </c>
       <c r="I77" s="1" t="s">
@@ -4189,7 +4189,7 @@
       <c r="G78" t="s">
         <v>8</v>
       </c>
-      <c r="H78">
+      <c r="H78" s="1">
         <v>19046</v>
       </c>
       <c r="I78" s="1" t="s">
@@ -4218,7 +4218,7 @@
       <c r="G79" t="s">
         <v>8</v>
       </c>
-      <c r="H79">
+      <c r="H79" s="1">
         <v>19046</v>
       </c>
       <c r="I79" s="1" t="s">
@@ -4247,7 +4247,7 @@
       <c r="G80" t="s">
         <v>8</v>
       </c>
-      <c r="H80">
+      <c r="H80" s="1">
         <v>19046</v>
       </c>
       <c r="I80" s="1" t="s">
@@ -4276,7 +4276,7 @@
       <c r="G81" t="s">
         <v>8</v>
       </c>
-      <c r="H81">
+      <c r="H81" s="1">
         <v>19046</v>
       </c>
       <c r="I81" s="1" t="s">
@@ -4305,7 +4305,7 @@
       <c r="G82" t="s">
         <v>8</v>
       </c>
-      <c r="H82">
+      <c r="H82" s="1">
         <v>19046</v>
       </c>
       <c r="I82" s="1" t="s">
@@ -4334,7 +4334,7 @@
       <c r="G83" t="s">
         <v>8</v>
       </c>
-      <c r="H83">
+      <c r="H83" s="1">
         <v>19046</v>
       </c>
       <c r="I83" s="1" t="s">
@@ -4363,7 +4363,7 @@
       <c r="G84" t="s">
         <v>8</v>
       </c>
-      <c r="H84">
+      <c r="H84" s="1">
         <v>19046</v>
       </c>
       <c r="I84" s="1" t="s">
@@ -4392,7 +4392,7 @@
       <c r="G85" t="s">
         <v>8</v>
       </c>
-      <c r="H85">
+      <c r="H85" s="1">
         <v>19046</v>
       </c>
       <c r="I85" s="1" t="s">
@@ -4421,7 +4421,7 @@
       <c r="G86" t="s">
         <v>8</v>
       </c>
-      <c r="H86">
+      <c r="H86" s="1">
         <v>19046</v>
       </c>
       <c r="I86" s="1" t="s">
@@ -4450,7 +4450,7 @@
       <c r="G87" t="s">
         <v>8</v>
       </c>
-      <c r="H87">
+      <c r="H87" s="1">
         <v>19046</v>
       </c>
       <c r="I87" s="1" t="s">
@@ -4479,7 +4479,7 @@
       <c r="G88" t="s">
         <v>8</v>
       </c>
-      <c r="H88">
+      <c r="H88" s="1">
         <v>19046</v>
       </c>
       <c r="I88" s="1" t="s">
@@ -4508,7 +4508,7 @@
       <c r="G89" t="s">
         <v>8</v>
       </c>
-      <c r="H89">
+      <c r="H89" s="1">
         <v>19046</v>
       </c>
       <c r="I89" s="1" t="s">
@@ -4537,7 +4537,7 @@
       <c r="G90" t="s">
         <v>8</v>
       </c>
-      <c r="H90">
+      <c r="H90" s="1">
         <v>19046</v>
       </c>
       <c r="I90" s="1" t="s">
@@ -4566,7 +4566,7 @@
       <c r="G91" t="s">
         <v>8</v>
       </c>
-      <c r="H91">
+      <c r="H91" s="1">
         <v>19046</v>
       </c>
       <c r="I91" s="1" t="s">
@@ -4595,7 +4595,7 @@
       <c r="G92" t="s">
         <v>8</v>
       </c>
-      <c r="H92">
+      <c r="H92" s="1">
         <v>19046</v>
       </c>
       <c r="I92" s="1" t="s">
@@ -4624,7 +4624,7 @@
       <c r="G93" t="s">
         <v>8</v>
       </c>
-      <c r="H93">
+      <c r="H93" s="1">
         <v>19046</v>
       </c>
       <c r="I93" s="1" t="s">
@@ -4653,7 +4653,7 @@
       <c r="G94" t="s">
         <v>8</v>
       </c>
-      <c r="H94">
+      <c r="H94" s="1">
         <v>19046</v>
       </c>
       <c r="I94" s="1" t="s">
@@ -4682,7 +4682,7 @@
       <c r="G95" t="s">
         <v>8</v>
       </c>
-      <c r="H95">
+      <c r="H95" s="1">
         <v>19046</v>
       </c>
       <c r="I95" s="1" t="s">
@@ -4711,7 +4711,7 @@
       <c r="G96" t="s">
         <v>8</v>
       </c>
-      <c r="H96">
+      <c r="H96" s="1">
         <v>19046</v>
       </c>
       <c r="I96" s="1" t="s">
@@ -4740,7 +4740,7 @@
       <c r="G97" t="s">
         <v>8</v>
       </c>
-      <c r="H97">
+      <c r="H97" s="1">
         <v>19046</v>
       </c>
       <c r="I97" s="1" t="s">
@@ -4769,7 +4769,7 @@
       <c r="G98" t="s">
         <v>8</v>
       </c>
-      <c r="H98">
+      <c r="H98" s="1">
         <v>19046</v>
       </c>
       <c r="I98" s="1" t="s">
@@ -4798,7 +4798,7 @@
       <c r="G99" t="s">
         <v>8</v>
       </c>
-      <c r="H99">
+      <c r="H99" s="1">
         <v>19046</v>
       </c>
       <c r="I99" s="1" t="s">
@@ -4827,7 +4827,7 @@
       <c r="G100" t="s">
         <v>8</v>
       </c>
-      <c r="H100">
+      <c r="H100" s="1">
         <v>19046</v>
       </c>
       <c r="I100" s="1" t="s">
@@ -4856,7 +4856,7 @@
       <c r="G101" t="s">
         <v>8</v>
       </c>
-      <c r="H101">
+      <c r="H101" s="1">
         <v>19046</v>
       </c>
       <c r="I101" s="1" t="s">
@@ -4885,7 +4885,7 @@
       <c r="G102" t="s">
         <v>8</v>
       </c>
-      <c r="H102">
+      <c r="H102" s="1">
         <v>19046</v>
       </c>
       <c r="I102" s="1" t="s">
@@ -4914,7 +4914,7 @@
       <c r="G103" t="s">
         <v>8</v>
       </c>
-      <c r="H103">
+      <c r="H103" s="1">
         <v>19046</v>
       </c>
       <c r="I103" s="1" t="s">
@@ -4943,7 +4943,7 @@
       <c r="G104" t="s">
         <v>8</v>
       </c>
-      <c r="H104">
+      <c r="H104" s="1">
         <v>19046</v>
       </c>
       <c r="I104" s="1" t="s">
@@ -4972,7 +4972,7 @@
       <c r="G105" t="s">
         <v>8</v>
       </c>
-      <c r="H105">
+      <c r="H105" s="1">
         <v>19046</v>
       </c>
       <c r="I105" s="1" t="s">
@@ -5001,7 +5001,7 @@
       <c r="G106" t="s">
         <v>8</v>
       </c>
-      <c r="H106">
+      <c r="H106" s="1">
         <v>19046</v>
       </c>
       <c r="I106" s="1" t="s">
@@ -5030,7 +5030,7 @@
       <c r="G107" t="s">
         <v>8</v>
       </c>
-      <c r="H107">
+      <c r="H107" s="1">
         <v>19046</v>
       </c>
       <c r="I107" s="1" t="s">
@@ -5059,7 +5059,7 @@
       <c r="G108" t="s">
         <v>8</v>
       </c>
-      <c r="H108">
+      <c r="H108" s="1">
         <v>19046</v>
       </c>
       <c r="I108" s="1" t="s">
@@ -5088,7 +5088,7 @@
       <c r="G109" t="s">
         <v>8</v>
       </c>
-      <c r="H109">
+      <c r="H109" s="1">
         <v>19046</v>
       </c>
       <c r="I109" s="1" t="s">
@@ -5117,7 +5117,7 @@
       <c r="G110" t="s">
         <v>8</v>
       </c>
-      <c r="H110">
+      <c r="H110" s="1">
         <v>19046</v>
       </c>
       <c r="I110" s="1" t="s">
@@ -5146,7 +5146,7 @@
       <c r="G111" t="s">
         <v>8</v>
       </c>
-      <c r="H111">
+      <c r="H111" s="1">
         <v>19046</v>
       </c>
       <c r="I111" s="1" t="s">
@@ -5175,7 +5175,7 @@
       <c r="G112" t="s">
         <v>8</v>
       </c>
-      <c r="H112">
+      <c r="H112" s="1">
         <v>19046</v>
       </c>
       <c r="I112" s="1" t="s">
@@ -5204,7 +5204,7 @@
       <c r="G113" t="s">
         <v>8</v>
       </c>
-      <c r="H113">
+      <c r="H113" s="1">
         <v>19046</v>
       </c>
       <c r="I113" s="1" t="s">
@@ -5233,7 +5233,7 @@
       <c r="G114" t="s">
         <v>8</v>
       </c>
-      <c r="H114">
+      <c r="H114" s="1">
         <v>19046</v>
       </c>
       <c r="I114" s="1" t="s">
@@ -5262,7 +5262,7 @@
       <c r="G115" t="s">
         <v>8</v>
       </c>
-      <c r="H115">
+      <c r="H115" s="1">
         <v>19046</v>
       </c>
       <c r="I115" s="1" t="s">
@@ -5291,7 +5291,7 @@
       <c r="G116" t="s">
         <v>8</v>
       </c>
-      <c r="H116">
+      <c r="H116" s="1">
         <v>19046</v>
       </c>
       <c r="I116" s="1" t="s">
@@ -5320,7 +5320,7 @@
       <c r="G117" t="s">
         <v>8</v>
       </c>
-      <c r="H117">
+      <c r="H117" s="1">
         <v>19046</v>
       </c>
       <c r="I117" s="1" t="s">
@@ -5349,7 +5349,7 @@
       <c r="G118" t="s">
         <v>8</v>
       </c>
-      <c r="H118">
+      <c r="H118" s="1">
         <v>19046</v>
       </c>
       <c r="I118" s="1" t="s">
@@ -5378,7 +5378,7 @@
       <c r="G119" t="s">
         <v>8</v>
       </c>
-      <c r="H119">
+      <c r="H119" s="1">
         <v>19046</v>
       </c>
       <c r="I119" s="1" t="s">
@@ -5407,7 +5407,7 @@
       <c r="G120" t="s">
         <v>8</v>
       </c>
-      <c r="H120">
+      <c r="H120" s="1">
         <v>19046</v>
       </c>
       <c r="I120" s="1" t="s">
@@ -5436,7 +5436,7 @@
       <c r="G121" t="s">
         <v>8</v>
       </c>
-      <c r="H121">
+      <c r="H121" s="1">
         <v>19046</v>
       </c>
       <c r="I121" s="1" t="s">
@@ -5465,7 +5465,7 @@
       <c r="G122" t="s">
         <v>8</v>
       </c>
-      <c r="H122">
+      <c r="H122" s="1">
         <v>19046</v>
       </c>
       <c r="I122" s="1" t="s">
@@ -5494,7 +5494,7 @@
       <c r="G123" t="s">
         <v>8</v>
       </c>
-      <c r="H123">
+      <c r="H123" s="1">
         <v>19046</v>
       </c>
       <c r="I123" s="1" t="s">
@@ -5523,7 +5523,7 @@
       <c r="G124" t="s">
         <v>8</v>
       </c>
-      <c r="H124">
+      <c r="H124" s="1">
         <v>19046</v>
       </c>
       <c r="I124" s="1" t="s">
@@ -5552,7 +5552,7 @@
       <c r="G125" t="s">
         <v>8</v>
       </c>
-      <c r="H125">
+      <c r="H125" s="1">
         <v>19046</v>
       </c>
       <c r="I125" s="1" t="s">
@@ -5581,7 +5581,7 @@
       <c r="G126" t="s">
         <v>8</v>
       </c>
-      <c r="H126">
+      <c r="H126" s="1">
         <v>19046</v>
       </c>
       <c r="I126" s="1" t="s">
@@ -5610,7 +5610,7 @@
       <c r="G127" t="s">
         <v>8</v>
       </c>
-      <c r="H127">
+      <c r="H127" s="1">
         <v>19046</v>
       </c>
       <c r="I127" s="1" t="s">
@@ -5639,7 +5639,7 @@
       <c r="G128" t="s">
         <v>8</v>
       </c>
-      <c r="H128">
+      <c r="H128" s="1">
         <v>19046</v>
       </c>
       <c r="I128" s="1" t="s">
@@ -5668,7 +5668,7 @@
       <c r="G129" t="s">
         <v>8</v>
       </c>
-      <c r="H129">
+      <c r="H129" s="1">
         <v>19046</v>
       </c>
       <c r="I129" s="1" t="s">
@@ -5697,7 +5697,7 @@
       <c r="G130" t="s">
         <v>8</v>
       </c>
-      <c r="H130">
+      <c r="H130" s="1">
         <v>19046</v>
       </c>
       <c r="I130" s="1" t="s">
@@ -5726,7 +5726,7 @@
       <c r="G131" t="s">
         <v>8</v>
       </c>
-      <c r="H131">
+      <c r="H131" s="1">
         <v>19046</v>
       </c>
       <c r="I131" s="1" t="s">
@@ -5755,7 +5755,7 @@
       <c r="G132" t="s">
         <v>8</v>
       </c>
-      <c r="H132">
+      <c r="H132" s="1">
         <v>19046</v>
       </c>
       <c r="I132" s="1" t="s">
@@ -5784,7 +5784,7 @@
       <c r="G133" t="s">
         <v>8</v>
       </c>
-      <c r="H133">
+      <c r="H133" s="1">
         <v>19046</v>
       </c>
       <c r="I133" s="1" t="s">
@@ -5813,7 +5813,7 @@
       <c r="G134" t="s">
         <v>8</v>
       </c>
-      <c r="H134">
+      <c r="H134" s="1">
         <v>19046</v>
       </c>
       <c r="I134" s="1" t="s">
@@ -5842,7 +5842,7 @@
       <c r="G135" t="s">
         <v>8</v>
       </c>
-      <c r="H135">
+      <c r="H135" s="1">
         <v>19046</v>
       </c>
       <c r="I135" s="1" t="s">
@@ -5871,7 +5871,7 @@
       <c r="G136" t="s">
         <v>8</v>
       </c>
-      <c r="H136">
+      <c r="H136" s="1">
         <v>19046</v>
       </c>
       <c r="I136" s="1" t="s">
@@ -5900,7 +5900,7 @@
       <c r="G137" t="s">
         <v>8</v>
       </c>
-      <c r="H137">
+      <c r="H137" s="1">
         <v>19046</v>
       </c>
       <c r="I137" s="1" t="s">
@@ -5929,7 +5929,7 @@
       <c r="G138" t="s">
         <v>8</v>
       </c>
-      <c r="H138">
+      <c r="H138" s="1">
         <v>19046</v>
       </c>
       <c r="I138" s="1" t="s">
@@ -5958,7 +5958,7 @@
       <c r="G139" t="s">
         <v>8</v>
       </c>
-      <c r="H139">
+      <c r="H139" s="1">
         <v>19046</v>
       </c>
       <c r="I139" s="1" t="s">
@@ -5987,7 +5987,7 @@
       <c r="G140" t="s">
         <v>8</v>
       </c>
-      <c r="H140">
+      <c r="H140" s="1">
         <v>19046</v>
       </c>
       <c r="I140" s="1" t="s">
@@ -6016,7 +6016,7 @@
       <c r="G141" t="s">
         <v>8</v>
       </c>
-      <c r="H141">
+      <c r="H141" s="1">
         <v>19046</v>
       </c>
       <c r="I141" s="1" t="s">
@@ -6045,7 +6045,7 @@
       <c r="G142" t="s">
         <v>8</v>
       </c>
-      <c r="H142">
+      <c r="H142" s="1">
         <v>19046</v>
       </c>
       <c r="I142" s="1" t="s">
@@ -6074,7 +6074,7 @@
       <c r="G143" t="s">
         <v>8</v>
       </c>
-      <c r="H143">
+      <c r="H143" s="1">
         <v>19046</v>
       </c>
       <c r="I143" s="1" t="s">
@@ -6103,7 +6103,7 @@
       <c r="G144" t="s">
         <v>8</v>
       </c>
-      <c r="H144">
+      <c r="H144" s="1">
         <v>19046</v>
       </c>
       <c r="I144" s="1" t="s">
@@ -6132,7 +6132,7 @@
       <c r="G145" t="s">
         <v>8</v>
       </c>
-      <c r="H145">
+      <c r="H145" s="1">
         <v>19046</v>
       </c>
       <c r="I145" s="1" t="s">
@@ -6161,7 +6161,7 @@
       <c r="G146" t="s">
         <v>8</v>
       </c>
-      <c r="H146">
+      <c r="H146" s="1">
         <v>19046</v>
       </c>
       <c r="I146" s="1" t="s">
@@ -6190,7 +6190,7 @@
       <c r="G147" t="s">
         <v>8</v>
       </c>
-      <c r="H147">
+      <c r="H147" s="1">
         <v>19046</v>
       </c>
       <c r="I147" s="1" t="s">
@@ -6219,7 +6219,7 @@
       <c r="G148" t="s">
         <v>8</v>
       </c>
-      <c r="H148">
+      <c r="H148" s="1">
         <v>19046</v>
       </c>
       <c r="I148" s="1" t="s">
@@ -6248,7 +6248,7 @@
       <c r="G149" t="s">
         <v>8</v>
       </c>
-      <c r="H149">
+      <c r="H149" s="1">
         <v>19046</v>
       </c>
       <c r="I149" s="1" t="s">
@@ -6277,7 +6277,7 @@
       <c r="G150" t="s">
         <v>8</v>
       </c>
-      <c r="H150">
+      <c r="H150" s="1">
         <v>19046</v>
       </c>
       <c r="I150" s="1" t="s">
@@ -6306,7 +6306,7 @@
       <c r="G151" t="s">
         <v>8</v>
       </c>
-      <c r="H151">
+      <c r="H151" s="1">
         <v>19046</v>
       </c>
       <c r="I151" s="1" t="s">
@@ -6335,7 +6335,7 @@
       <c r="G152" t="s">
         <v>8</v>
       </c>
-      <c r="H152">
+      <c r="H152" s="1">
         <v>19046</v>
       </c>
       <c r="I152" s="1" t="s">
@@ -6364,7 +6364,7 @@
       <c r="G153" t="s">
         <v>8</v>
       </c>
-      <c r="H153">
+      <c r="H153" s="1">
         <v>19046</v>
       </c>
       <c r="I153" s="1" t="s">
@@ -6393,7 +6393,7 @@
       <c r="G154" t="s">
         <v>8</v>
       </c>
-      <c r="H154">
+      <c r="H154" s="1">
         <v>19046</v>
       </c>
       <c r="I154" s="1" t="s">
@@ -6422,7 +6422,7 @@
       <c r="G155" t="s">
         <v>8</v>
       </c>
-      <c r="H155">
+      <c r="H155" s="1">
         <v>19046</v>
       </c>
       <c r="I155" s="1" t="s">
@@ -6451,7 +6451,7 @@
       <c r="G156" t="s">
         <v>8</v>
       </c>
-      <c r="H156">
+      <c r="H156" s="1">
         <v>19046</v>
       </c>
       <c r="I156" s="1" t="s">
@@ -6480,7 +6480,7 @@
       <c r="G157" t="s">
         <v>8</v>
       </c>
-      <c r="H157">
+      <c r="H157" s="1">
         <v>19046</v>
       </c>
       <c r="I157" s="1" t="s">
@@ -6509,7 +6509,7 @@
       <c r="G158" t="s">
         <v>8</v>
       </c>
-      <c r="H158">
+      <c r="H158" s="1">
         <v>19046</v>
       </c>
       <c r="I158" s="1" t="s">
@@ -6538,7 +6538,7 @@
       <c r="G159" t="s">
         <v>8</v>
       </c>
-      <c r="H159">
+      <c r="H159" s="1">
         <v>19046</v>
       </c>
       <c r="I159" s="1" t="s">
@@ -6567,7 +6567,7 @@
       <c r="G160" t="s">
         <v>8</v>
       </c>
-      <c r="H160">
+      <c r="H160" s="1">
         <v>19046</v>
       </c>
       <c r="I160" s="1" t="s">
@@ -6596,7 +6596,7 @@
       <c r="G161" t="s">
         <v>8</v>
       </c>
-      <c r="H161">
+      <c r="H161" s="1">
         <v>19046</v>
       </c>
       <c r="I161" s="1" t="s">
@@ -6625,7 +6625,7 @@
       <c r="G162" t="s">
         <v>8</v>
       </c>
-      <c r="H162">
+      <c r="H162" s="1">
         <v>19046</v>
       </c>
       <c r="I162" s="1" t="s">
@@ -6654,7 +6654,7 @@
       <c r="G163" t="s">
         <v>8</v>
       </c>
-      <c r="H163">
+      <c r="H163" s="1">
         <v>19046</v>
       </c>
       <c r="I163" s="1" t="s">
@@ -6683,7 +6683,7 @@
       <c r="G164" t="s">
         <v>8</v>
       </c>
-      <c r="H164">
+      <c r="H164" s="1">
         <v>19046</v>
       </c>
       <c r="I164" s="1" t="s">
@@ -6712,7 +6712,7 @@
       <c r="G165" t="s">
         <v>8</v>
       </c>
-      <c r="H165">
+      <c r="H165" s="1">
         <v>19046</v>
       </c>
       <c r="I165" s="1" t="s">
@@ -6741,7 +6741,7 @@
       <c r="G166" t="s">
         <v>8</v>
       </c>
-      <c r="H166">
+      <c r="H166" s="1">
         <v>19046</v>
       </c>
       <c r="I166" s="1" t="s">
@@ -6770,7 +6770,7 @@
       <c r="G167" t="s">
         <v>8</v>
       </c>
-      <c r="H167">
+      <c r="H167" s="1">
         <v>19046</v>
       </c>
       <c r="I167" s="1" t="s">
@@ -6799,7 +6799,7 @@
       <c r="G168" t="s">
         <v>8</v>
       </c>
-      <c r="H168">
+      <c r="H168" s="1">
         <v>19046</v>
       </c>
       <c r="I168" s="1" t="s">
@@ -6828,7 +6828,7 @@
       <c r="G169" t="s">
         <v>8</v>
       </c>
-      <c r="H169">
+      <c r="H169" s="1">
         <v>19046</v>
       </c>
       <c r="I169" s="1" t="s">
@@ -6857,7 +6857,7 @@
       <c r="G170" t="s">
         <v>8</v>
       </c>
-      <c r="H170">
+      <c r="H170" s="1">
         <v>19046</v>
       </c>
       <c r="I170" s="1" t="s">
@@ -6886,7 +6886,7 @@
       <c r="G171" t="s">
         <v>8</v>
       </c>
-      <c r="H171">
+      <c r="H171" s="1">
         <v>19046</v>
       </c>
       <c r="I171" s="1" t="s">
@@ -6915,7 +6915,7 @@
       <c r="G172" t="s">
         <v>8</v>
       </c>
-      <c r="H172">
+      <c r="H172" s="1">
         <v>19046</v>
       </c>
       <c r="I172" s="1" t="s">
@@ -6944,7 +6944,7 @@
       <c r="G173" t="s">
         <v>8</v>
       </c>
-      <c r="H173">
+      <c r="H173" s="1">
         <v>19046</v>
       </c>
       <c r="I173" s="1" t="s">
@@ -6973,7 +6973,7 @@
       <c r="G174" t="s">
         <v>8</v>
       </c>
-      <c r="H174">
+      <c r="H174" s="1">
         <v>19046</v>
       </c>
       <c r="I174" s="1" t="s">
@@ -7002,7 +7002,7 @@
       <c r="G175" t="s">
         <v>8</v>
       </c>
-      <c r="H175">
+      <c r="H175" s="1">
         <v>19046</v>
       </c>
       <c r="I175" s="1" t="s">
@@ -7031,7 +7031,7 @@
       <c r="G176" t="s">
         <v>8</v>
       </c>
-      <c r="H176">
+      <c r="H176" s="1">
         <v>19046</v>
       </c>
       <c r="I176" s="1" t="s">
@@ -7060,7 +7060,7 @@
       <c r="G177" t="s">
         <v>8</v>
       </c>
-      <c r="H177">
+      <c r="H177" s="1">
         <v>19046</v>
       </c>
       <c r="I177" s="1" t="s">
@@ -7089,7 +7089,7 @@
       <c r="G178" t="s">
         <v>8</v>
       </c>
-      <c r="H178">
+      <c r="H178" s="1">
         <v>19046</v>
       </c>
       <c r="I178" s="1" t="s">
@@ -7118,7 +7118,7 @@
       <c r="G179" t="s">
         <v>8</v>
       </c>
-      <c r="H179">
+      <c r="H179" s="1">
         <v>19046</v>
       </c>
       <c r="I179" s="1" t="s">
@@ -7147,7 +7147,7 @@
       <c r="G180" t="s">
         <v>8</v>
       </c>
-      <c r="H180">
+      <c r="H180" s="1">
         <v>19046</v>
       </c>
       <c r="I180" s="1" t="s">
@@ -7176,7 +7176,7 @@
       <c r="G181" t="s">
         <v>8</v>
       </c>
-      <c r="H181">
+      <c r="H181" s="1">
         <v>19046</v>
       </c>
       <c r="I181" s="1" t="s">
@@ -7205,7 +7205,7 @@
       <c r="G182" t="s">
         <v>8</v>
       </c>
-      <c r="H182">
+      <c r="H182" s="1">
         <v>19046</v>
       </c>
       <c r="I182" s="1" t="s">
@@ -7234,7 +7234,7 @@
       <c r="G183" t="s">
         <v>8</v>
       </c>
-      <c r="H183">
+      <c r="H183" s="1">
         <v>19046</v>
       </c>
       <c r="I183" s="1" t="s">
@@ -7263,7 +7263,7 @@
       <c r="G184" t="s">
         <v>8</v>
       </c>
-      <c r="H184">
+      <c r="H184" s="1">
         <v>19046</v>
       </c>
       <c r="I184" s="1" t="s">
@@ -7292,7 +7292,7 @@
       <c r="G185" t="s">
         <v>8</v>
       </c>
-      <c r="H185">
+      <c r="H185" s="1">
         <v>19046</v>
       </c>
       <c r="I185" s="1" t="s">
@@ -7321,7 +7321,7 @@
       <c r="G186" t="s">
         <v>8</v>
       </c>
-      <c r="H186">
+      <c r="H186" s="1">
         <v>19046</v>
       </c>
       <c r="I186" s="1" t="s">
@@ -7350,7 +7350,7 @@
       <c r="G187" t="s">
         <v>8</v>
       </c>
-      <c r="H187">
+      <c r="H187" s="1">
         <v>19046</v>
       </c>
       <c r="I187" s="1" t="s">
@@ -7379,7 +7379,7 @@
       <c r="G188" t="s">
         <v>8</v>
       </c>
-      <c r="H188">
+      <c r="H188" s="1">
         <v>19046</v>
       </c>
       <c r="I188" s="1" t="s">
@@ -7408,7 +7408,7 @@
       <c r="G189" t="s">
         <v>8</v>
       </c>
-      <c r="H189">
+      <c r="H189" s="1">
         <v>19046</v>
       </c>
       <c r="I189" s="1" t="s">
@@ -7437,7 +7437,7 @@
       <c r="G190" t="s">
         <v>8</v>
       </c>
-      <c r="H190">
+      <c r="H190" s="1">
         <v>19046</v>
       </c>
       <c r="I190" s="1" t="s">
@@ -7466,7 +7466,7 @@
       <c r="G191" t="s">
         <v>8</v>
       </c>
-      <c r="H191">
+      <c r="H191" s="1">
         <v>19046</v>
       </c>
       <c r="I191" s="1" t="s">
@@ -7495,7 +7495,7 @@
       <c r="G192" t="s">
         <v>8</v>
       </c>
-      <c r="H192">
+      <c r="H192" s="1">
         <v>19046</v>
       </c>
       <c r="I192" s="1" t="s">
@@ -7524,7 +7524,7 @@
       <c r="G193" t="s">
         <v>8</v>
       </c>
-      <c r="H193">
+      <c r="H193" s="1">
         <v>19046</v>
       </c>
       <c r="I193" s="1" t="s">
@@ -7553,7 +7553,7 @@
       <c r="G194" t="s">
         <v>8</v>
       </c>
-      <c r="H194">
+      <c r="H194" s="1">
         <v>19046</v>
       </c>
       <c r="I194" s="1" t="s">
@@ -7582,7 +7582,7 @@
       <c r="G195" t="s">
         <v>8</v>
       </c>
-      <c r="H195">
+      <c r="H195" s="1">
         <v>19046</v>
       </c>
       <c r="I195" s="1" t="s">
@@ -7611,7 +7611,7 @@
       <c r="G196" t="s">
         <v>8</v>
       </c>
-      <c r="H196">
+      <c r="H196" s="1">
         <v>19046</v>
       </c>
       <c r="I196" s="1" t="s">
@@ -7640,7 +7640,7 @@
       <c r="G197" t="s">
         <v>8</v>
       </c>
-      <c r="H197">
+      <c r="H197" s="1">
         <v>19046</v>
       </c>
       <c r="I197" s="1" t="s">
@@ -7669,7 +7669,7 @@
       <c r="G198" t="s">
         <v>8</v>
       </c>
-      <c r="H198">
+      <c r="H198" s="1">
         <v>19046</v>
       </c>
       <c r="I198" s="1" t="s">
@@ -7698,7 +7698,7 @@
       <c r="G199" t="s">
         <v>8</v>
       </c>
-      <c r="H199">
+      <c r="H199" s="1">
         <v>19046</v>
       </c>
       <c r="I199" s="1" t="s">
@@ -7727,7 +7727,7 @@
       <c r="G200" t="s">
         <v>8</v>
       </c>
-      <c r="H200">
+      <c r="H200" s="1">
         <v>19046</v>
       </c>
       <c r="I200" s="1" t="s">
@@ -7756,7 +7756,7 @@
       <c r="G201" t="s">
         <v>8</v>
       </c>
-      <c r="H201">
+      <c r="H201" s="1">
         <v>19046</v>
       </c>
       <c r="I201" s="1" t="s">
@@ -7785,7 +7785,7 @@
       <c r="G202" t="s">
         <v>8</v>
       </c>
-      <c r="H202">
+      <c r="H202" s="1">
         <v>19046</v>
       </c>
       <c r="I202" s="1" t="s">
@@ -7814,7 +7814,7 @@
       <c r="G203" t="s">
         <v>8</v>
       </c>
-      <c r="H203">
+      <c r="H203" s="1">
         <v>19046</v>
       </c>
       <c r="I203" s="1" t="s">
@@ -7843,7 +7843,7 @@
       <c r="G204" t="s">
         <v>8</v>
       </c>
-      <c r="H204">
+      <c r="H204" s="1">
         <v>19046</v>
       </c>
       <c r="I204" s="1" t="s">
@@ -7872,7 +7872,7 @@
       <c r="G205" t="s">
         <v>8</v>
       </c>
-      <c r="H205">
+      <c r="H205" s="1">
         <v>19046</v>
       </c>
       <c r="I205" s="1" t="s">
@@ -7901,7 +7901,7 @@
       <c r="G206" t="s">
         <v>8</v>
       </c>
-      <c r="H206">
+      <c r="H206" s="1">
         <v>19046</v>
       </c>
       <c r="I206" s="1" t="s">
@@ -7930,7 +7930,7 @@
       <c r="G207" t="s">
         <v>8</v>
       </c>
-      <c r="H207">
+      <c r="H207" s="1">
         <v>19046</v>
       </c>
       <c r="I207" s="1" t="s">
@@ -7959,7 +7959,7 @@
       <c r="G208" t="s">
         <v>8</v>
       </c>
-      <c r="H208">
+      <c r="H208" s="1">
         <v>19046</v>
       </c>
       <c r="I208" s="1" t="s">
@@ -7988,7 +7988,7 @@
       <c r="G209" t="s">
         <v>8</v>
       </c>
-      <c r="H209">
+      <c r="H209" s="1">
         <v>19046</v>
       </c>
       <c r="I209" s="1" t="s">
@@ -8017,7 +8017,7 @@
       <c r="G210" t="s">
         <v>8</v>
       </c>
-      <c r="H210">
+      <c r="H210" s="1">
         <v>19046</v>
       </c>
       <c r="I210" s="1" t="s">
@@ -8046,7 +8046,7 @@
       <c r="G211" t="s">
         <v>8</v>
       </c>
-      <c r="H211">
+      <c r="H211" s="1">
         <v>19046</v>
       </c>
       <c r="I211" s="1" t="s">
@@ -8075,7 +8075,7 @@
       <c r="G212" t="s">
         <v>8</v>
       </c>
-      <c r="H212">
+      <c r="H212" s="1">
         <v>19046</v>
       </c>
       <c r="I212" s="1" t="s">
@@ -8104,7 +8104,7 @@
       <c r="G213" t="s">
         <v>8</v>
       </c>
-      <c r="H213">
+      <c r="H213" s="1">
         <v>19046</v>
       </c>
       <c r="I213" s="1" t="s">
@@ -8133,7 +8133,7 @@
       <c r="G214" t="s">
         <v>8</v>
       </c>
-      <c r="H214">
+      <c r="H214" s="1">
         <v>19046</v>
       </c>
       <c r="I214" s="1" t="s">
@@ -8162,7 +8162,7 @@
       <c r="G215" t="s">
         <v>8</v>
       </c>
-      <c r="H215">
+      <c r="H215" s="1">
         <v>19046</v>
       </c>
       <c r="I215" s="1" t="s">
@@ -8191,7 +8191,7 @@
       <c r="G216" t="s">
         <v>8</v>
       </c>
-      <c r="H216">
+      <c r="H216" s="1">
         <v>19046</v>
       </c>
       <c r="I216" s="1" t="s">
@@ -8220,7 +8220,7 @@
       <c r="G217" t="s">
         <v>8</v>
       </c>
-      <c r="H217">
+      <c r="H217" s="1">
         <v>19046</v>
       </c>
       <c r="I217" s="1" t="s">
@@ -8249,7 +8249,7 @@
       <c r="G218" t="s">
         <v>8</v>
       </c>
-      <c r="H218">
+      <c r="H218" s="1">
         <v>19046</v>
       </c>
       <c r="I218" s="1" t="s">
@@ -8278,7 +8278,7 @@
       <c r="G219" t="s">
         <v>8</v>
       </c>
-      <c r="H219">
+      <c r="H219" s="1">
         <v>19046</v>
       </c>
       <c r="I219" s="1" t="s">
@@ -8307,7 +8307,7 @@
       <c r="G220" t="s">
         <v>8</v>
       </c>
-      <c r="H220">
+      <c r="H220" s="1">
         <v>19046</v>
       </c>
       <c r="I220" s="1" t="s">
@@ -8336,7 +8336,7 @@
       <c r="G221" t="s">
         <v>8</v>
       </c>
-      <c r="H221">
+      <c r="H221" s="1">
         <v>19046</v>
       </c>
       <c r="I221" s="1" t="s">
@@ -8365,7 +8365,7 @@
       <c r="G222" t="s">
         <v>8</v>
       </c>
-      <c r="H222">
+      <c r="H222" s="1">
         <v>19046</v>
       </c>
       <c r="I222" s="1" t="s">
@@ -8394,7 +8394,7 @@
       <c r="G223" t="s">
         <v>8</v>
       </c>
-      <c r="H223">
+      <c r="H223" s="1">
         <v>19046</v>
       </c>
       <c r="I223" s="1" t="s">
@@ -8423,7 +8423,7 @@
       <c r="G224" t="s">
         <v>8</v>
       </c>
-      <c r="H224">
+      <c r="H224" s="1">
         <v>19046</v>
       </c>
       <c r="I224" s="1" t="s">
@@ -8452,7 +8452,7 @@
       <c r="G225" t="s">
         <v>8</v>
       </c>
-      <c r="H225">
+      <c r="H225" s="1">
         <v>19046</v>
       </c>
       <c r="I225" s="1" t="s">
@@ -8481,7 +8481,7 @@
       <c r="G226" t="s">
         <v>8</v>
       </c>
-      <c r="H226">
+      <c r="H226" s="1">
         <v>19046</v>
       </c>
       <c r="I226" s="1" t="s">
@@ -8510,7 +8510,7 @@
       <c r="G227" t="s">
         <v>8</v>
       </c>
-      <c r="H227">
+      <c r="H227" s="1">
         <v>19046</v>
       </c>
       <c r="I227" s="1" t="s">
@@ -8539,7 +8539,7 @@
       <c r="G228" t="s">
         <v>8</v>
       </c>
-      <c r="H228">
+      <c r="H228" s="1">
         <v>19046</v>
       </c>
       <c r="I228" s="1" t="s">
@@ -8568,7 +8568,7 @@
       <c r="G229" t="s">
         <v>8</v>
       </c>
-      <c r="H229">
+      <c r="H229" s="1">
         <v>19046</v>
       </c>
       <c r="I229" s="1" t="s">
@@ -8597,7 +8597,7 @@
       <c r="G230" t="s">
         <v>8</v>
       </c>
-      <c r="H230">
+      <c r="H230" s="1">
         <v>19046</v>
       </c>
       <c r="I230" s="1" t="s">
@@ -8626,7 +8626,7 @@
       <c r="G231" t="s">
         <v>8</v>
       </c>
-      <c r="H231">
+      <c r="H231" s="1">
         <v>19046</v>
       </c>
       <c r="I231" s="1" t="s">
@@ -8655,7 +8655,7 @@
       <c r="G232" t="s">
         <v>8</v>
       </c>
-      <c r="H232">
+      <c r="H232" s="1">
         <v>19046</v>
       </c>
       <c r="I232" s="1" t="s">
@@ -8684,7 +8684,7 @@
       <c r="G233" t="s">
         <v>8</v>
       </c>
-      <c r="H233">
+      <c r="H233" s="1">
         <v>19046</v>
       </c>
       <c r="I233" s="1" t="s">
@@ -8713,7 +8713,7 @@
       <c r="G234" t="s">
         <v>8</v>
       </c>
-      <c r="H234">
+      <c r="H234" s="1">
         <v>19046</v>
       </c>
       <c r="I234" s="1" t="s">
@@ -8742,7 +8742,7 @@
       <c r="G235" t="s">
         <v>8</v>
       </c>
-      <c r="H235">
+      <c r="H235" s="1">
         <v>19046</v>
       </c>
       <c r="I235" s="1" t="s">
@@ -8771,7 +8771,7 @@
       <c r="G236" t="s">
         <v>8</v>
       </c>
-      <c r="H236">
+      <c r="H236" s="1">
         <v>19046</v>
       </c>
       <c r="I236" s="1" t="s">
@@ -8800,7 +8800,7 @@
       <c r="G237" t="s">
         <v>8</v>
       </c>
-      <c r="H237">
+      <c r="H237" s="1">
         <v>19046</v>
       </c>
       <c r="I237" s="1" t="s">
@@ -8829,7 +8829,7 @@
       <c r="G238" t="s">
         <v>8</v>
       </c>
-      <c r="H238">
+      <c r="H238" s="1">
         <v>19046</v>
       </c>
       <c r="I238" s="1" t="s">
@@ -8858,7 +8858,7 @@
       <c r="G239" t="s">
         <v>8</v>
       </c>
-      <c r="H239">
+      <c r="H239" s="1">
         <v>19046</v>
       </c>
       <c r="I239" s="1" t="s">
@@ -8887,7 +8887,7 @@
       <c r="G240" t="s">
         <v>8</v>
       </c>
-      <c r="H240">
+      <c r="H240" s="1">
         <v>19046</v>
       </c>
       <c r="I240" s="1" t="s">
@@ -8916,7 +8916,7 @@
       <c r="G241" t="s">
         <v>8</v>
       </c>
-      <c r="H241">
+      <c r="H241" s="1">
         <v>19046</v>
       </c>
       <c r="I241" s="1" t="s">
@@ -8945,7 +8945,7 @@
       <c r="G242" t="s">
         <v>8</v>
       </c>
-      <c r="H242">
+      <c r="H242" s="1">
         <v>19046</v>
       </c>
       <c r="I242" s="1" t="s">
@@ -8974,7 +8974,7 @@
       <c r="G243" t="s">
         <v>8</v>
       </c>
-      <c r="H243">
+      <c r="H243" s="1">
         <v>19046</v>
       </c>
       <c r="I243" s="1" t="s">
@@ -9003,7 +9003,7 @@
       <c r="G244" t="s">
         <v>8</v>
       </c>
-      <c r="H244">
+      <c r="H244" s="1">
         <v>19046</v>
       </c>
       <c r="I244" s="1" t="s">
@@ -9032,7 +9032,7 @@
       <c r="G245" t="s">
         <v>8</v>
       </c>
-      <c r="H245">
+      <c r="H245" s="1">
         <v>19046</v>
       </c>
       <c r="I245" s="1" t="s">
@@ -9061,7 +9061,7 @@
       <c r="G246" t="s">
         <v>8</v>
       </c>
-      <c r="H246">
+      <c r="H246" s="1">
         <v>19046</v>
       </c>
       <c r="I246" s="1" t="s">
@@ -9090,7 +9090,7 @@
       <c r="G247" t="s">
         <v>8</v>
       </c>
-      <c r="H247">
+      <c r="H247" s="1">
         <v>19046</v>
       </c>
       <c r="I247" s="1" t="s">
@@ -9119,7 +9119,7 @@
       <c r="G248" t="s">
         <v>8</v>
       </c>
-      <c r="H248">
+      <c r="H248" s="1">
         <v>19046</v>
       </c>
       <c r="I248" s="1" t="s">
@@ -9148,7 +9148,7 @@
       <c r="G249" t="s">
         <v>8</v>
       </c>
-      <c r="H249">
+      <c r="H249" s="1">
         <v>19046</v>
       </c>
       <c r="I249" s="1" t="s">
@@ -9177,7 +9177,7 @@
       <c r="G250" t="s">
         <v>8</v>
       </c>
-      <c r="H250">
+      <c r="H250" s="1">
         <v>19046</v>
       </c>
       <c r="I250" s="1" t="s">
@@ -9206,7 +9206,7 @@
       <c r="G251" t="s">
         <v>8</v>
       </c>
-      <c r="H251">
+      <c r="H251" s="1">
         <v>19046</v>
       </c>
       <c r="I251" s="1" t="s">
@@ -9235,7 +9235,7 @@
       <c r="G252" t="s">
         <v>8</v>
       </c>
-      <c r="H252">
+      <c r="H252" s="1">
         <v>19046</v>
       </c>
       <c r="I252" s="1" t="s">
@@ -9264,7 +9264,7 @@
       <c r="G253" t="s">
         <v>8</v>
       </c>
-      <c r="H253">
+      <c r="H253" s="1">
         <v>19046</v>
       </c>
       <c r="I253" s="1" t="s">
@@ -9293,7 +9293,7 @@
       <c r="G254" t="s">
         <v>8</v>
       </c>
-      <c r="H254">
+      <c r="H254" s="1">
         <v>19046</v>
       </c>
       <c r="I254" s="1" t="s">
@@ -9322,7 +9322,7 @@
       <c r="G255" t="s">
         <v>8</v>
       </c>
-      <c r="H255">
+      <c r="H255" s="1">
         <v>19046</v>
       </c>
       <c r="I255" s="1" t="s">
@@ -9351,7 +9351,7 @@
       <c r="G256" t="s">
         <v>8</v>
       </c>
-      <c r="H256">
+      <c r="H256" s="1">
         <v>19046</v>
       </c>
       <c r="I256" s="1" t="s">
@@ -9380,7 +9380,7 @@
       <c r="G257" t="s">
         <v>8</v>
       </c>
-      <c r="H257">
+      <c r="H257" s="1">
         <v>19046</v>
       </c>
       <c r="I257" s="1" t="s">
@@ -9409,7 +9409,7 @@
       <c r="G258" t="s">
         <v>8</v>
       </c>
-      <c r="H258">
+      <c r="H258" s="1">
         <v>19046</v>
       </c>
       <c r="I258" s="1" t="s">
@@ -9438,7 +9438,7 @@
       <c r="G259" t="s">
         <v>8</v>
       </c>
-      <c r="H259">
+      <c r="H259" s="1">
         <v>19046</v>
       </c>
       <c r="I259" s="1" t="s">
@@ -9467,7 +9467,7 @@
       <c r="G260" t="s">
         <v>8</v>
       </c>
-      <c r="H260">
+      <c r="H260" s="1">
         <v>19046</v>
       </c>
       <c r="I260" s="1" t="s">
@@ -9496,7 +9496,7 @@
       <c r="G261" t="s">
         <v>8</v>
       </c>
-      <c r="H261">
+      <c r="H261" s="1">
         <v>19046</v>
       </c>
       <c r="I261" s="1" t="s">
@@ -9525,7 +9525,7 @@
       <c r="G262" t="s">
         <v>8</v>
       </c>
-      <c r="H262">
+      <c r="H262" s="1">
         <v>19046</v>
       </c>
       <c r="I262" s="1" t="s">
@@ -9554,7 +9554,7 @@
       <c r="G263" t="s">
         <v>8</v>
       </c>
-      <c r="H263">
+      <c r="H263" s="1">
         <v>19046</v>
       </c>
       <c r="I263" s="1" t="s">
@@ -9583,7 +9583,7 @@
       <c r="G264" t="s">
         <v>8</v>
       </c>
-      <c r="H264">
+      <c r="H264" s="1">
         <v>19046</v>
       </c>
       <c r="I264" s="1" t="s">
@@ -9612,7 +9612,7 @@
       <c r="G265" t="s">
         <v>8</v>
       </c>
-      <c r="H265">
+      <c r="H265" s="1">
         <v>19046</v>
       </c>
       <c r="I265" s="1" t="s">
@@ -9641,7 +9641,7 @@
       <c r="G266" t="s">
         <v>8</v>
       </c>
-      <c r="H266">
+      <c r="H266" s="1">
         <v>19046</v>
       </c>
       <c r="I266" s="1" t="s">
@@ -9670,7 +9670,7 @@
       <c r="G267" t="s">
         <v>8</v>
       </c>
-      <c r="H267">
+      <c r="H267" s="1">
         <v>19046</v>
       </c>
       <c r="I267" s="1" t="s">
@@ -9699,7 +9699,7 @@
       <c r="G268" t="s">
         <v>8</v>
       </c>
-      <c r="H268">
+      <c r="H268" s="1">
         <v>19046</v>
       </c>
       <c r="I268" s="1" t="s">
@@ -9728,7 +9728,7 @@
       <c r="G269" t="s">
         <v>8</v>
       </c>
-      <c r="H269">
+      <c r="H269" s="1">
         <v>19046</v>
       </c>
       <c r="I269" s="1" t="s">
@@ -9757,7 +9757,7 @@
       <c r="G270" t="s">
         <v>8</v>
       </c>
-      <c r="H270">
+      <c r="H270" s="1">
         <v>19046</v>
       </c>
       <c r="I270" s="1" t="s">
@@ -9786,7 +9786,7 @@
       <c r="G271" t="s">
         <v>8</v>
       </c>
-      <c r="H271">
+      <c r="H271" s="1">
         <v>19046</v>
       </c>
       <c r="I271" s="1" t="s">
@@ -9815,7 +9815,7 @@
       <c r="G272" t="s">
         <v>8</v>
       </c>
-      <c r="H272">
+      <c r="H272" s="1">
         <v>19046</v>
       </c>
       <c r="I272" s="1" t="s">
@@ -9844,7 +9844,7 @@
       <c r="G273" t="s">
         <v>8</v>
       </c>
-      <c r="H273">
+      <c r="H273" s="1">
         <v>19046</v>
       </c>
       <c r="I273" s="1" t="s">
@@ -9873,7 +9873,7 @@
       <c r="G274" t="s">
         <v>8</v>
       </c>
-      <c r="H274">
+      <c r="H274" s="1">
         <v>19046</v>
       </c>
       <c r="I274" s="1" t="s">
@@ -9902,7 +9902,7 @@
       <c r="G275" t="s">
         <v>8</v>
       </c>
-      <c r="H275">
+      <c r="H275" s="1">
         <v>19046</v>
       </c>
       <c r="I275" s="1" t="s">
@@ -9931,7 +9931,7 @@
       <c r="G276" t="s">
         <v>8</v>
       </c>
-      <c r="H276">
+      <c r="H276" s="1">
         <v>19046</v>
       </c>
       <c r="I276" s="1" t="s">
@@ -9960,7 +9960,7 @@
       <c r="G277" t="s">
         <v>8</v>
       </c>
-      <c r="H277">
+      <c r="H277" s="1">
         <v>19046</v>
       </c>
       <c r="I277" s="1" t="s">
@@ -9989,7 +9989,7 @@
       <c r="G278" t="s">
         <v>8</v>
       </c>
-      <c r="H278">
+      <c r="H278" s="1">
         <v>19046</v>
       </c>
       <c r="I278" s="1" t="s">
@@ -10018,7 +10018,7 @@
       <c r="G279" t="s">
         <v>8</v>
       </c>
-      <c r="H279">
+      <c r="H279" s="1">
         <v>19046</v>
       </c>
       <c r="I279" s="1" t="s">
@@ -10047,7 +10047,7 @@
       <c r="G280" t="s">
         <v>8</v>
       </c>
-      <c r="H280">
+      <c r="H280" s="1">
         <v>19046</v>
       </c>
       <c r="I280" s="1" t="s">
@@ -10076,7 +10076,7 @@
       <c r="G281" t="s">
         <v>8</v>
       </c>
-      <c r="H281">
+      <c r="H281" s="1">
         <v>19046</v>
       </c>
       <c r="I281" s="1" t="s">
@@ -10105,7 +10105,7 @@
       <c r="G282" t="s">
         <v>8</v>
       </c>
-      <c r="H282">
+      <c r="H282" s="1">
         <v>19046</v>
       </c>
       <c r="I282" s="1" t="s">
@@ -10134,7 +10134,7 @@
       <c r="G283" t="s">
         <v>8</v>
       </c>
-      <c r="H283">
+      <c r="H283" s="1">
         <v>19046</v>
       </c>
       <c r="I283" s="1" t="s">
@@ -10163,7 +10163,7 @@
       <c r="G284" t="s">
         <v>8</v>
       </c>
-      <c r="H284">
+      <c r="H284" s="1">
         <v>19046</v>
       </c>
       <c r="I284" s="1" t="s">
@@ -10192,7 +10192,7 @@
       <c r="G285" t="s">
         <v>8</v>
       </c>
-      <c r="H285">
+      <c r="H285" s="1">
         <v>19046</v>
       </c>
       <c r="I285" s="1" t="s">
@@ -10221,7 +10221,7 @@
       <c r="G286" t="s">
         <v>8</v>
       </c>
-      <c r="H286">
+      <c r="H286" s="1">
         <v>19046</v>
       </c>
       <c r="I286" s="1" t="s">
@@ -10250,7 +10250,7 @@
       <c r="G287" t="s">
         <v>8</v>
       </c>
-      <c r="H287">
+      <c r="H287" s="1">
         <v>19046</v>
       </c>
       <c r="I287" s="1" t="s">
@@ -10279,7 +10279,7 @@
       <c r="G288" t="s">
         <v>8</v>
       </c>
-      <c r="H288">
+      <c r="H288" s="1">
         <v>19046</v>
       </c>
       <c r="I288" s="1" t="s">
@@ -10308,7 +10308,7 @@
       <c r="G289" t="s">
         <v>8</v>
       </c>
-      <c r="H289">
+      <c r="H289" s="1">
         <v>19046</v>
       </c>
       <c r="I289" s="1" t="s">
@@ -10337,7 +10337,7 @@
       <c r="G290" t="s">
         <v>8</v>
       </c>
-      <c r="H290">
+      <c r="H290" s="1">
         <v>19046</v>
       </c>
       <c r="I290" s="1" t="s">
@@ -10366,7 +10366,7 @@
       <c r="G291" t="s">
         <v>8</v>
       </c>
-      <c r="H291">
+      <c r="H291" s="1">
         <v>19046</v>
       </c>
       <c r="I291" s="1" t="s">
@@ -10395,7 +10395,7 @@
       <c r="G292" t="s">
         <v>8</v>
       </c>
-      <c r="H292">
+      <c r="H292" s="1">
         <v>19046</v>
       </c>
       <c r="I292" s="1" t="s">
@@ -10424,7 +10424,7 @@
       <c r="G293" t="s">
         <v>8</v>
       </c>
-      <c r="H293">
+      <c r="H293" s="1">
         <v>19046</v>
       </c>
       <c r="I293" s="1" t="s">
@@ -10453,7 +10453,7 @@
       <c r="G294" t="s">
         <v>8</v>
       </c>
-      <c r="H294">
+      <c r="H294" s="1">
         <v>19046</v>
       </c>
       <c r="I294" s="1" t="s">
@@ -10482,7 +10482,7 @@
       <c r="G295" t="s">
         <v>8</v>
       </c>
-      <c r="H295">
+      <c r="H295" s="1">
         <v>19046</v>
       </c>
       <c r="I295" s="1" t="s">
@@ -10511,7 +10511,7 @@
       <c r="G296" t="s">
         <v>8</v>
       </c>
-      <c r="H296">
+      <c r="H296" s="1">
         <v>19046</v>
       </c>
       <c r="I296" s="1" t="s">
@@ -10540,7 +10540,7 @@
       <c r="G297" t="s">
         <v>8</v>
       </c>
-      <c r="H297">
+      <c r="H297" s="1">
         <v>19046</v>
       </c>
       <c r="I297" s="1" t="s">
@@ -10569,7 +10569,7 @@
       <c r="G298" t="s">
         <v>8</v>
       </c>
-      <c r="H298">
+      <c r="H298" s="1">
         <v>19046</v>
       </c>
       <c r="I298" s="1" t="s">
@@ -10598,7 +10598,7 @@
       <c r="G299" t="s">
         <v>8</v>
       </c>
-      <c r="H299">
+      <c r="H299" s="1">
         <v>19046</v>
       </c>
       <c r="I299" s="1" t="s">
@@ -10627,7 +10627,7 @@
       <c r="G300" t="s">
         <v>8</v>
       </c>
-      <c r="H300">
+      <c r="H300" s="1">
         <v>19046</v>
       </c>
       <c r="I300" s="1" t="s">
@@ -10656,7 +10656,7 @@
       <c r="G301" t="s">
         <v>8</v>
       </c>
-      <c r="H301">
+      <c r="H301" s="1">
         <v>19046</v>
       </c>
       <c r="I301" s="1" t="s">
@@ -10685,7 +10685,7 @@
       <c r="G302" t="s">
         <v>8</v>
       </c>
-      <c r="H302">
+      <c r="H302" s="1">
         <v>19046</v>
       </c>
       <c r="I302" s="1" t="s">
@@ -10714,7 +10714,7 @@
       <c r="G303" t="s">
         <v>8</v>
       </c>
-      <c r="H303">
+      <c r="H303" s="1">
         <v>19046</v>
       </c>
       <c r="I303" s="1" t="s">
@@ -10743,7 +10743,7 @@
       <c r="G304" t="s">
         <v>8</v>
       </c>
-      <c r="H304">
+      <c r="H304" s="1">
         <v>19046</v>
       </c>
       <c r="I304" s="1" t="s">
@@ -10772,7 +10772,7 @@
       <c r="G305" t="s">
         <v>8</v>
       </c>
-      <c r="H305">
+      <c r="H305" s="1">
         <v>19046</v>
       </c>
       <c r="I305" s="1" t="s">
@@ -10801,7 +10801,7 @@
       <c r="G306" t="s">
         <v>8</v>
       </c>
-      <c r="H306">
+      <c r="H306" s="1">
         <v>19046</v>
       </c>
       <c r="I306" s="1" t="s">
@@ -10830,7 +10830,7 @@
       <c r="G307" t="s">
         <v>8</v>
       </c>
-      <c r="H307">
+      <c r="H307" s="1">
         <v>19046</v>
       </c>
       <c r="I307" s="1" t="s">
@@ -10859,7 +10859,7 @@
       <c r="G308" t="s">
         <v>8</v>
       </c>
-      <c r="H308">
+      <c r="H308" s="1">
         <v>19046</v>
       </c>
       <c r="I308" s="1" t="s">
@@ -10888,7 +10888,7 @@
       <c r="G309" t="s">
         <v>8</v>
       </c>
-      <c r="H309">
+      <c r="H309" s="1">
         <v>19046</v>
       </c>
       <c r="I309" s="1" t="s">
@@ -10917,7 +10917,7 @@
       <c r="G310" t="s">
         <v>8</v>
       </c>
-      <c r="H310">
+      <c r="H310" s="1">
         <v>19046</v>
       </c>
       <c r="I310" s="1" t="s">
@@ -10946,7 +10946,7 @@
       <c r="G311" t="s">
         <v>8</v>
       </c>
-      <c r="H311">
+      <c r="H311" s="1">
         <v>19046</v>
       </c>
       <c r="I311" s="1" t="s">
@@ -10975,7 +10975,7 @@
       <c r="G312" t="s">
         <v>8</v>
       </c>
-      <c r="H312">
+      <c r="H312" s="1">
         <v>19046</v>
       </c>
       <c r="I312" s="1" t="s">
@@ -11004,7 +11004,7 @@
       <c r="G313" t="s">
         <v>8</v>
       </c>
-      <c r="H313">
+      <c r="H313" s="1">
         <v>19046</v>
       </c>
       <c r="I313" s="1" t="s">
@@ -11033,7 +11033,7 @@
       <c r="G314" t="s">
         <v>8</v>
       </c>
-      <c r="H314">
+      <c r="H314" s="1">
         <v>19046</v>
       </c>
       <c r="I314" s="1" t="s">
@@ -11062,7 +11062,7 @@
       <c r="G315" t="s">
         <v>8</v>
       </c>
-      <c r="H315">
+      <c r="H315" s="1">
         <v>19046</v>
       </c>
       <c r="I315" s="1" t="s">
@@ -11091,7 +11091,7 @@
       <c r="G316" t="s">
         <v>8</v>
       </c>
-      <c r="H316">
+      <c r="H316" s="1">
         <v>19046</v>
       </c>
       <c r="I316" s="1" t="s">
@@ -11120,7 +11120,7 @@
       <c r="G317" t="s">
         <v>8</v>
       </c>
-      <c r="H317">
+      <c r="H317" s="1">
         <v>19046</v>
       </c>
       <c r="I317" s="1" t="s">
@@ -11149,7 +11149,7 @@
       <c r="G318" t="s">
         <v>8</v>
       </c>
-      <c r="H318">
+      <c r="H318" s="1">
         <v>19046</v>
       </c>
       <c r="I318" s="1" t="s">
@@ -11178,7 +11178,7 @@
       <c r="G319" t="s">
         <v>8</v>
       </c>
-      <c r="H319">
+      <c r="H319" s="1">
         <v>19046</v>
       </c>
       <c r="I319" s="1" t="s">
@@ -11207,7 +11207,7 @@
       <c r="G320" t="s">
         <v>8</v>
       </c>
-      <c r="H320">
+      <c r="H320" s="1">
         <v>19046</v>
       </c>
       <c r="I320" s="1" t="s">
@@ -11236,7 +11236,7 @@
       <c r="G321" t="s">
         <v>8</v>
       </c>
-      <c r="H321">
+      <c r="H321" s="1">
         <v>19046</v>
       </c>
       <c r="I321" s="1" t="s">
@@ -11265,7 +11265,7 @@
       <c r="G322" t="s">
         <v>8</v>
       </c>
-      <c r="H322">
+      <c r="H322" s="1">
         <v>19046</v>
       </c>
       <c r="I322" s="1" t="s">
@@ -11294,7 +11294,7 @@
       <c r="G323" t="s">
         <v>8</v>
       </c>
-      <c r="H323">
+      <c r="H323" s="1">
         <v>19046</v>
       </c>
       <c r="I323" s="1" t="s">
@@ -11323,7 +11323,7 @@
       <c r="G324" t="s">
         <v>8</v>
       </c>
-      <c r="H324">
+      <c r="H324" s="1">
         <v>19046</v>
       </c>
       <c r="I324" s="1" t="s">
@@ -11352,7 +11352,7 @@
       <c r="G325" t="s">
         <v>8</v>
       </c>
-      <c r="H325">
+      <c r="H325" s="1">
         <v>19046</v>
       </c>
       <c r="I325" s="1" t="s">
@@ -11381,7 +11381,7 @@
       <c r="G326" t="s">
         <v>8</v>
       </c>
-      <c r="H326">
+      <c r="H326" s="1">
         <v>19046</v>
       </c>
       <c r="I326" s="1" t="s">
@@ -11410,7 +11410,7 @@
       <c r="G327" t="s">
         <v>8</v>
       </c>
-      <c r="H327">
+      <c r="H327" s="1">
         <v>19046</v>
       </c>
       <c r="I327" s="1" t="s">
@@ -11439,7 +11439,7 @@
       <c r="G328" t="s">
         <v>8</v>
       </c>
-      <c r="H328">
+      <c r="H328" s="1">
         <v>19046</v>
       </c>
       <c r="I328" s="1" t="s">
@@ -11468,7 +11468,7 @@
       <c r="G329" t="s">
         <v>8</v>
       </c>
-      <c r="H329">
+      <c r="H329" s="1">
         <v>19046</v>
       </c>
       <c r="I329" s="1" t="s">
@@ -11497,7 +11497,7 @@
       <c r="G330" t="s">
         <v>8</v>
       </c>
-      <c r="H330">
+      <c r="H330" s="1">
         <v>19046</v>
       </c>
       <c r="I330" s="1" t="s">
@@ -11526,7 +11526,7 @@
       <c r="G331" t="s">
         <v>8</v>
       </c>
-      <c r="H331">
+      <c r="H331" s="1">
         <v>19046</v>
       </c>
       <c r="I331" s="1" t="s">
@@ -11555,7 +11555,7 @@
       <c r="G332" t="s">
         <v>8</v>
       </c>
-      <c r="H332">
+      <c r="H332" s="1">
         <v>19046</v>
       </c>
       <c r="I332" s="1" t="s">
@@ -11584,7 +11584,7 @@
       <c r="G333" t="s">
         <v>8</v>
       </c>
-      <c r="H333">
+      <c r="H333" s="1">
         <v>19046</v>
       </c>
       <c r="I333" s="1" t="s">
@@ -11613,7 +11613,7 @@
       <c r="G334" t="s">
         <v>8</v>
       </c>
-      <c r="H334">
+      <c r="H334" s="1">
         <v>19046</v>
       </c>
       <c r="I334" s="1" t="s">
@@ -11642,7 +11642,7 @@
       <c r="G335" t="s">
         <v>8</v>
       </c>
-      <c r="H335">
+      <c r="H335" s="1">
         <v>19046</v>
       </c>
       <c r="I335" s="1" t="s">
@@ -11671,7 +11671,7 @@
       <c r="G336" t="s">
         <v>8</v>
       </c>
-      <c r="H336">
+      <c r="H336" s="1">
         <v>19046</v>
       </c>
       <c r="I336" s="1" t="s">
@@ -11700,7 +11700,7 @@
       <c r="G337" t="s">
         <v>8</v>
       </c>
-      <c r="H337">
+      <c r="H337" s="1">
         <v>19046</v>
       </c>
       <c r="I337" s="1" t="s">
@@ -11729,7 +11729,7 @@
       <c r="G338" t="s">
         <v>8</v>
       </c>
-      <c r="H338">
+      <c r="H338" s="1">
         <v>19046</v>
       </c>
       <c r="I338" s="1" t="s">
@@ -11758,7 +11758,7 @@
       <c r="G339" t="s">
         <v>8</v>
       </c>
-      <c r="H339">
+      <c r="H339" s="1">
         <v>19046</v>
       </c>
       <c r="I339" s="1" t="s">
@@ -11787,7 +11787,7 @@
       <c r="G340" t="s">
         <v>8</v>
       </c>
-      <c r="H340">
+      <c r="H340" s="1">
         <v>19046</v>
       </c>
       <c r="I340" s="1" t="s">
@@ -11816,7 +11816,7 @@
       <c r="G341" t="s">
         <v>8</v>
       </c>
-      <c r="H341">
+      <c r="H341" s="1">
         <v>19046</v>
       </c>
       <c r="I341" s="1" t="s">
@@ -11845,7 +11845,7 @@
       <c r="G342" t="s">
         <v>8</v>
       </c>
-      <c r="H342">
+      <c r="H342" s="1">
         <v>19046</v>
       </c>
       <c r="I342" s="1" t="s">
@@ -11874,7 +11874,7 @@
       <c r="G343" t="s">
         <v>8</v>
       </c>
-      <c r="H343">
+      <c r="H343" s="1">
         <v>19046</v>
       </c>
       <c r="I343" s="1" t="s">
@@ -11903,7 +11903,7 @@
       <c r="G344" t="s">
         <v>8</v>
       </c>
-      <c r="H344">
+      <c r="H344" s="1">
         <v>19046</v>
       </c>
       <c r="I344" s="1" t="s">
@@ -11932,7 +11932,7 @@
       <c r="G345" t="s">
         <v>8</v>
       </c>
-      <c r="H345">
+      <c r="H345" s="1">
         <v>19046</v>
       </c>
       <c r="I345" s="1" t="s">
@@ -11961,7 +11961,7 @@
       <c r="G346" t="s">
         <v>8</v>
       </c>
-      <c r="H346">
+      <c r="H346" s="1">
         <v>19046</v>
       </c>
       <c r="I346" s="1" t="s">
@@ -11990,7 +11990,7 @@
       <c r="G347" t="s">
         <v>8</v>
       </c>
-      <c r="H347">
+      <c r="H347" s="1">
         <v>19046</v>
       </c>
       <c r="I347" s="1" t="s">
@@ -12019,7 +12019,7 @@
       <c r="G348" t="s">
         <v>8</v>
       </c>
-      <c r="H348">
+      <c r="H348" s="1">
         <v>19046</v>
       </c>
       <c r="I348" s="1" t="s">
@@ -12048,7 +12048,7 @@
       <c r="G349" t="s">
         <v>8</v>
       </c>
-      <c r="H349">
+      <c r="H349" s="1">
         <v>19046</v>
       </c>
       <c r="I349" s="1" t="s">
@@ -12077,7 +12077,7 @@
       <c r="G350" t="s">
         <v>8</v>
       </c>
-      <c r="H350">
+      <c r="H350" s="1">
         <v>19046</v>
       </c>
       <c r="I350" s="1" t="s">
@@ -12106,7 +12106,7 @@
       <c r="G351" t="s">
         <v>8</v>
       </c>
-      <c r="H351">
+      <c r="H351" s="1">
         <v>19046</v>
       </c>
       <c r="I351" s="1" t="s">
@@ -12135,7 +12135,7 @@
       <c r="G352" t="s">
         <v>8</v>
       </c>
-      <c r="H352">
+      <c r="H352" s="1">
         <v>19046</v>
       </c>
       <c r="I352" s="1" t="s">
@@ -12164,7 +12164,7 @@
       <c r="G353" t="s">
         <v>8</v>
       </c>
-      <c r="H353">
+      <c r="H353" s="1">
         <v>19046</v>
       </c>
       <c r="I353" s="1" t="s">
@@ -12193,7 +12193,7 @@
       <c r="G354" t="s">
         <v>8</v>
       </c>
-      <c r="H354">
+      <c r="H354" s="1">
         <v>19046</v>
       </c>
       <c r="I354" s="1" t="s">
@@ -12222,7 +12222,7 @@
       <c r="G355" t="s">
         <v>8</v>
       </c>
-      <c r="H355">
+      <c r="H355" s="1">
         <v>19046</v>
       </c>
       <c r="I355" s="1" t="s">
@@ -12251,7 +12251,7 @@
       <c r="G356" t="s">
         <v>8</v>
       </c>
-      <c r="H356">
+      <c r="H356" s="1">
         <v>19046</v>
       </c>
       <c r="I356" s="1" t="s">
@@ -12280,7 +12280,7 @@
       <c r="G357" t="s">
         <v>8</v>
       </c>
-      <c r="H357">
+      <c r="H357" s="1">
         <v>19046</v>
       </c>
       <c r="I357" s="1" t="s">
@@ -12309,7 +12309,7 @@
       <c r="G358" t="s">
         <v>8</v>
       </c>
-      <c r="H358">
+      <c r="H358" s="1">
         <v>19046</v>
       </c>
       <c r="I358" s="1" t="s">
@@ -12338,7 +12338,7 @@
       <c r="G359" t="s">
         <v>8</v>
       </c>
-      <c r="H359">
+      <c r="H359" s="1">
         <v>19046</v>
       </c>
       <c r="I359" s="1" t="s">
@@ -12367,7 +12367,7 @@
       <c r="G360" t="s">
         <v>8</v>
       </c>
-      <c r="H360">
+      <c r="H360" s="1">
         <v>19046</v>
       </c>
       <c r="I360" s="1" t="s">
@@ -12396,7 +12396,7 @@
       <c r="G361" t="s">
         <v>8</v>
       </c>
-      <c r="H361">
+      <c r="H361" s="1">
         <v>19046</v>
       </c>
       <c r="I361" s="1" t="s">
@@ -12425,7 +12425,7 @@
       <c r="G362" t="s">
         <v>8</v>
       </c>
-      <c r="H362">
+      <c r="H362" s="1">
         <v>19046</v>
       </c>
       <c r="I362" s="1" t="s">
@@ -12454,7 +12454,7 @@
       <c r="G363" t="s">
         <v>8</v>
       </c>
-      <c r="H363">
+      <c r="H363" s="1">
         <v>19046</v>
       </c>
       <c r="I363" s="1" t="s">
@@ -12483,7 +12483,7 @@
       <c r="G364" t="s">
         <v>8</v>
       </c>
-      <c r="H364">
+      <c r="H364" s="1">
         <v>19046</v>
       </c>
       <c r="I364" s="1" t="s">
@@ -12512,7 +12512,7 @@
       <c r="G365" t="s">
         <v>8</v>
       </c>
-      <c r="H365">
+      <c r="H365" s="1">
         <v>19046</v>
       </c>
       <c r="I365" s="1" t="s">
@@ -12541,7 +12541,7 @@
       <c r="G366" t="s">
         <v>8</v>
       </c>
-      <c r="H366">
+      <c r="H366" s="1">
         <v>19046</v>
       </c>
       <c r="I366" s="1" t="s">
@@ -12570,7 +12570,7 @@
       <c r="G367" t="s">
         <v>8</v>
       </c>
-      <c r="H367">
+      <c r="H367" s="1">
         <v>19046</v>
       </c>
       <c r="I367" s="1" t="s">
@@ -12599,7 +12599,7 @@
       <c r="G368" t="s">
         <v>8</v>
       </c>
-      <c r="H368">
+      <c r="H368" s="1">
         <v>19046</v>
       </c>
       <c r="I368" s="1" t="s">
@@ -12628,7 +12628,7 @@
       <c r="G369" t="s">
         <v>8</v>
       </c>
-      <c r="H369">
+      <c r="H369" s="1">
         <v>19046</v>
       </c>
       <c r="I369" s="1" t="s">
@@ -12657,7 +12657,7 @@
       <c r="G370" t="s">
         <v>8</v>
       </c>
-      <c r="H370">
+      <c r="H370" s="1">
         <v>19046</v>
       </c>
       <c r="I370" s="1" t="s">
@@ -12686,7 +12686,7 @@
       <c r="G371" t="s">
         <v>8</v>
       </c>
-      <c r="H371">
+      <c r="H371" s="1">
         <v>19046</v>
       </c>
       <c r="I371" s="1" t="s">
@@ -12715,7 +12715,7 @@
       <c r="G372" t="s">
         <v>8</v>
       </c>
-      <c r="H372">
+      <c r="H372" s="1">
         <v>19046</v>
       </c>
       <c r="I372" s="1" t="s">
@@ -12744,7 +12744,7 @@
       <c r="G373" t="s">
         <v>8</v>
       </c>
-      <c r="H373">
+      <c r="H373" s="1">
         <v>19046</v>
       </c>
       <c r="I373" s="1" t="s">
@@ -12773,7 +12773,7 @@
       <c r="G374" t="s">
         <v>8</v>
       </c>
-      <c r="H374">
+      <c r="H374" s="1">
         <v>19046</v>
       </c>
       <c r="I374" s="1" t="s">
@@ -12802,7 +12802,7 @@
       <c r="G375" t="s">
         <v>8</v>
       </c>
-      <c r="H375">
+      <c r="H375" s="1">
         <v>19046</v>
       </c>
       <c r="I375" s="1" t="s">
@@ -12831,7 +12831,7 @@
       <c r="G376" t="s">
         <v>8</v>
       </c>
-      <c r="H376">
+      <c r="H376" s="1">
         <v>19046</v>
       </c>
       <c r="I376" s="1" t="s">
@@ -12860,7 +12860,7 @@
       <c r="G377" t="s">
         <v>8</v>
       </c>
-      <c r="H377">
+      <c r="H377" s="1">
         <v>19046</v>
       </c>
       <c r="I377" s="1" t="s">
@@ -12889,7 +12889,7 @@
       <c r="G378" t="s">
         <v>8</v>
       </c>
-      <c r="H378">
+      <c r="H378" s="1">
         <v>19046</v>
       </c>
       <c r="I378" s="1" t="s">
@@ -12918,7 +12918,7 @@
       <c r="G379" t="s">
         <v>8</v>
       </c>
-      <c r="H379">
+      <c r="H379" s="1">
         <v>19046</v>
       </c>
       <c r="I379" s="1" t="s">
@@ -12947,7 +12947,7 @@
       <c r="G380" t="s">
         <v>8</v>
       </c>
-      <c r="H380">
+      <c r="H380" s="1">
         <v>19046</v>
       </c>
       <c r="I380" s="1" t="s">
@@ -12976,7 +12976,7 @@
       <c r="G381" t="s">
         <v>8</v>
       </c>
-      <c r="H381">
+      <c r="H381" s="1">
         <v>19046</v>
       </c>
       <c r="I381" s="1" t="s">
@@ -13005,7 +13005,7 @@
       <c r="G382" t="s">
         <v>8</v>
       </c>
-      <c r="H382">
+      <c r="H382" s="1">
         <v>19046</v>
       </c>
       <c r="I382" s="1" t="s">
@@ -13034,7 +13034,7 @@
       <c r="G383" t="s">
         <v>8</v>
       </c>
-      <c r="H383">
+      <c r="H383" s="1">
         <v>19046</v>
       </c>
       <c r="I383" s="1" t="s">
@@ -13063,7 +13063,7 @@
       <c r="G384" t="s">
         <v>8</v>
       </c>
-      <c r="H384">
+      <c r="H384" s="1">
         <v>19046</v>
       </c>
       <c r="I384" s="1" t="s">
@@ -13092,7 +13092,7 @@
       <c r="G385" t="s">
         <v>8</v>
       </c>
-      <c r="H385">
+      <c r="H385" s="1">
         <v>19046</v>
       </c>
       <c r="I385" s="1" t="s">
@@ -13121,7 +13121,7 @@
       <c r="G386" t="s">
         <v>8</v>
       </c>
-      <c r="H386">
+      <c r="H386" s="1">
         <v>19046</v>
       </c>
       <c r="I386" s="1" t="s">
@@ -13150,7 +13150,7 @@
       <c r="G387" t="s">
         <v>8</v>
       </c>
-      <c r="H387">
+      <c r="H387" s="1">
         <v>19046</v>
       </c>
       <c r="I387" s="1" t="s">
@@ -13179,7 +13179,7 @@
       <c r="G388" t="s">
         <v>8</v>
       </c>
-      <c r="H388">
+      <c r="H388" s="1">
         <v>19046</v>
       </c>
       <c r="I388" s="1" t="s">
@@ -13208,7 +13208,7 @@
       <c r="G389" t="s">
         <v>8</v>
       </c>
-      <c r="H389">
+      <c r="H389" s="1">
         <v>19046</v>
       </c>
       <c r="I389" s="1" t="s">
@@ -13237,7 +13237,7 @@
       <c r="G390" t="s">
         <v>8</v>
       </c>
-      <c r="H390">
+      <c r="H390" s="1">
         <v>19046</v>
       </c>
       <c r="I390" s="1" t="s">
@@ -13266,7 +13266,7 @@
       <c r="G391" t="s">
         <v>8</v>
       </c>
-      <c r="H391">
+      <c r="H391" s="1">
         <v>19046</v>
       </c>
       <c r="I391" s="1" t="s">
@@ -13295,7 +13295,7 @@
       <c r="G392" t="s">
         <v>8</v>
       </c>
-      <c r="H392">
+      <c r="H392" s="1">
         <v>19046</v>
       </c>
       <c r="I392" s="1" t="s">
@@ -13324,7 +13324,7 @@
       <c r="G393" t="s">
         <v>8</v>
       </c>
-      <c r="H393">
+      <c r="H393" s="1">
         <v>19046</v>
       </c>
       <c r="I393" s="1" t="s">
@@ -13353,7 +13353,7 @@
       <c r="G394" t="s">
         <v>8</v>
       </c>
-      <c r="H394">
+      <c r="H394" s="1">
         <v>19046</v>
       </c>
       <c r="I394" s="1" t="s">
@@ -13382,7 +13382,7 @@
       <c r="G395" t="s">
         <v>8</v>
       </c>
-      <c r="H395">
+      <c r="H395" s="1">
         <v>19046</v>
       </c>
       <c r="I395" s="1" t="s">
@@ -13411,7 +13411,7 @@
       <c r="G396" t="s">
         <v>8</v>
       </c>
-      <c r="H396">
+      <c r="H396" s="1">
         <v>19046</v>
       </c>
       <c r="I396" s="1" t="s">
@@ -13440,7 +13440,7 @@
       <c r="G397" t="s">
         <v>8</v>
       </c>
-      <c r="H397">
+      <c r="H397" s="1">
         <v>19046</v>
       </c>
       <c r="I397" s="1" t="s">
@@ -13469,7 +13469,7 @@
       <c r="G398" t="s">
         <v>8</v>
       </c>
-      <c r="H398">
+      <c r="H398" s="1">
         <v>19046</v>
       </c>
       <c r="I398" s="1" t="s">
@@ -13498,7 +13498,7 @@
       <c r="G399" t="s">
         <v>8</v>
       </c>
-      <c r="H399">
+      <c r="H399" s="1">
         <v>19046</v>
       </c>
       <c r="I399" s="1" t="s">
@@ -13527,7 +13527,7 @@
       <c r="G400" t="s">
         <v>8</v>
       </c>
-      <c r="H400">
+      <c r="H400" s="1">
         <v>19046</v>
       </c>
       <c r="I400" s="1" t="s">
@@ -13556,7 +13556,7 @@
       <c r="G401" t="s">
         <v>8</v>
       </c>
-      <c r="H401">
+      <c r="H401" s="1">
         <v>19046</v>
       </c>
       <c r="I401" s="1" t="s">
@@ -13585,7 +13585,7 @@
       <c r="G402" t="s">
         <v>8</v>
       </c>
-      <c r="H402">
+      <c r="H402" s="1">
         <v>19046</v>
       </c>
       <c r="I402" s="1" t="s">
@@ -13614,7 +13614,7 @@
       <c r="G403" t="s">
         <v>8</v>
       </c>
-      <c r="H403">
+      <c r="H403" s="1">
         <v>19046</v>
       </c>
       <c r="I403" s="1" t="s">
@@ -13643,7 +13643,7 @@
       <c r="G404" t="s">
         <v>8</v>
       </c>
-      <c r="H404">
+      <c r="H404" s="1">
         <v>19046</v>
       </c>
       <c r="I404" s="1" t="s">
@@ -13672,7 +13672,7 @@
       <c r="G405" t="s">
         <v>8</v>
       </c>
-      <c r="H405">
+      <c r="H405" s="1">
         <v>19046</v>
       </c>
       <c r="I405" s="1" t="s">
@@ -13701,7 +13701,7 @@
       <c r="G406" t="s">
         <v>8</v>
       </c>
-      <c r="H406">
+      <c r="H406" s="1">
         <v>19046</v>
       </c>
       <c r="I406" s="1" t="s">
@@ -13730,7 +13730,7 @@
       <c r="G407" t="s">
         <v>8</v>
       </c>
-      <c r="H407">
+      <c r="H407" s="1">
         <v>19046</v>
       </c>
       <c r="I407" s="1" t="s">
@@ -13759,7 +13759,7 @@
       <c r="G408" t="s">
         <v>8</v>
       </c>
-      <c r="H408">
+      <c r="H408" s="1">
         <v>19046</v>
       </c>
       <c r="I408" s="1" t="s">
@@ -13788,7 +13788,7 @@
       <c r="G409" t="s">
         <v>8</v>
       </c>
-      <c r="H409">
+      <c r="H409" s="1">
         <v>19046</v>
       </c>
       <c r="I409" s="1" t="s">
@@ -13817,7 +13817,7 @@
       <c r="G410" t="s">
         <v>8</v>
       </c>
-      <c r="H410">
+      <c r="H410" s="1">
         <v>19046</v>
       </c>
       <c r="I410" s="1" t="s">
@@ -13846,7 +13846,7 @@
       <c r="G411" t="s">
         <v>8</v>
       </c>
-      <c r="H411">
+      <c r="H411" s="1">
         <v>19046</v>
       </c>
       <c r="I411" s="1" t="s">
@@ -13875,7 +13875,7 @@
       <c r="G412" t="s">
         <v>8</v>
       </c>
-      <c r="H412">
+      <c r="H412" s="1">
         <v>19046</v>
       </c>
       <c r="I412" s="1" t="s">
@@ -13904,7 +13904,7 @@
       <c r="G413" t="s">
         <v>8</v>
       </c>
-      <c r="H413">
+      <c r="H413" s="1">
         <v>19046</v>
       </c>
       <c r="I413" s="1" t="s">
@@ -13933,7 +13933,7 @@
       <c r="G414" t="s">
         <v>8</v>
       </c>
-      <c r="H414">
+      <c r="H414" s="1">
         <v>19046</v>
       </c>
       <c r="I414" s="1" t="s">
@@ -13962,7 +13962,7 @@
       <c r="G415" t="s">
         <v>8</v>
       </c>
-      <c r="H415">
+      <c r="H415" s="1">
         <v>19046</v>
       </c>
       <c r="I415" s="1" t="s">
@@ -13991,7 +13991,7 @@
       <c r="G416" t="s">
         <v>8</v>
       </c>
-      <c r="H416">
+      <c r="H416" s="1">
         <v>19046</v>
       </c>
       <c r="I416" s="1" t="s">
@@ -14020,7 +14020,7 @@
       <c r="G417" t="s">
         <v>8</v>
       </c>
-      <c r="H417">
+      <c r="H417" s="1">
         <v>19046</v>
       </c>
       <c r="I417" s="1" t="s">
@@ -14049,7 +14049,7 @@
       <c r="G418" t="s">
         <v>8</v>
       </c>
-      <c r="H418">
+      <c r="H418" s="1">
         <v>19046</v>
       </c>
       <c r="I418" s="1" t="s">
@@ -14078,7 +14078,7 @@
       <c r="G419" t="s">
         <v>8</v>
       </c>
-      <c r="H419">
+      <c r="H419" s="1">
         <v>19046</v>
       </c>
       <c r="I419" s="1" t="s">
@@ -14107,7 +14107,7 @@
       <c r="G420" t="s">
         <v>8</v>
       </c>
-      <c r="H420">
+      <c r="H420" s="1">
         <v>19046</v>
       </c>
       <c r="I420" s="1" t="s">
@@ -14136,7 +14136,7 @@
       <c r="G421" t="s">
         <v>8</v>
       </c>
-      <c r="H421">
+      <c r="H421" s="1">
         <v>19046</v>
       </c>
       <c r="I421" s="1" t="s">
@@ -14165,7 +14165,7 @@
       <c r="G422" t="s">
         <v>8</v>
       </c>
-      <c r="H422">
+      <c r="H422" s="1">
         <v>19046</v>
       </c>
       <c r="I422" s="1" t="s">
@@ -14194,7 +14194,7 @@
       <c r="G423" t="s">
         <v>8</v>
       </c>
-      <c r="H423">
+      <c r="H423" s="1">
         <v>19046</v>
       </c>
       <c r="I423" s="1" t="s">
@@ -14223,7 +14223,7 @@
       <c r="G424" t="s">
         <v>8</v>
       </c>
-      <c r="H424">
+      <c r="H424" s="1">
         <v>19046</v>
       </c>
       <c r="I424" s="1" t="s">
@@ -14252,7 +14252,7 @@
       <c r="G425" t="s">
         <v>8</v>
       </c>
-      <c r="H425">
+      <c r="H425" s="1">
         <v>19046</v>
       </c>
       <c r="I425" s="1" t="s">
@@ -14281,7 +14281,7 @@
       <c r="G426" t="s">
         <v>8</v>
       </c>
-      <c r="H426">
+      <c r="H426" s="1">
         <v>19046</v>
       </c>
       <c r="I426" s="1" t="s">
@@ -14310,7 +14310,7 @@
       <c r="G427" t="s">
         <v>8</v>
       </c>
-      <c r="H427">
+      <c r="H427" s="1">
         <v>19046</v>
       </c>
       <c r="I427" s="1" t="s">
@@ -14339,7 +14339,7 @@
       <c r="G428" t="s">
         <v>8</v>
       </c>
-      <c r="H428">
+      <c r="H428" s="1">
         <v>19046</v>
       </c>
       <c r="I428" s="1" t="s">
@@ -14368,7 +14368,7 @@
       <c r="G429" t="s">
         <v>8</v>
       </c>
-      <c r="H429">
+      <c r="H429" s="1">
         <v>19046</v>
       </c>
       <c r="I429" s="1" t="s">
@@ -14397,7 +14397,7 @@
       <c r="G430" t="s">
         <v>8</v>
       </c>
-      <c r="H430">
+      <c r="H430" s="1">
         <v>19046</v>
       </c>
       <c r="I430" s="1" t="s">
@@ -14426,7 +14426,7 @@
       <c r="G431" t="s">
         <v>8</v>
       </c>
-      <c r="H431">
+      <c r="H431" s="1">
         <v>19046</v>
       </c>
       <c r="I431" s="1" t="s">
@@ -14455,7 +14455,7 @@
       <c r="G432" t="s">
         <v>8</v>
       </c>
-      <c r="H432">
+      <c r="H432" s="1">
         <v>19046</v>
       </c>
       <c r="I432" s="1" t="s">
@@ -14484,7 +14484,7 @@
       <c r="G433" t="s">
         <v>8</v>
       </c>
-      <c r="H433">
+      <c r="H433" s="1">
         <v>19046</v>
       </c>
       <c r="I433" s="1" t="s">
@@ -14513,7 +14513,7 @@
       <c r="G434" t="s">
         <v>8</v>
       </c>
-      <c r="H434">
+      <c r="H434" s="1">
         <v>19046</v>
       </c>
       <c r="I434" s="1" t="s">
@@ -14542,7 +14542,7 @@
       <c r="G435" t="s">
         <v>8</v>
       </c>
-      <c r="H435">
+      <c r="H435" s="1">
         <v>19046</v>
       </c>
       <c r="I435" s="1" t="s">
@@ -14571,7 +14571,7 @@
       <c r="G436" t="s">
         <v>8</v>
       </c>
-      <c r="H436">
+      <c r="H436" s="1">
         <v>19046</v>
       </c>
       <c r="I436" s="1" t="s">
@@ -14600,7 +14600,7 @@
       <c r="G437" t="s">
         <v>8</v>
       </c>
-      <c r="H437">
+      <c r="H437" s="1">
         <v>19046</v>
       </c>
       <c r="I437" s="1" t="s">
@@ -14629,7 +14629,7 @@
       <c r="G438" t="s">
         <v>8</v>
       </c>
-      <c r="H438">
+      <c r="H438" s="1">
         <v>19046</v>
       </c>
       <c r="I438" s="1" t="s">
@@ -14658,7 +14658,7 @@
       <c r="G439" t="s">
         <v>8</v>
       </c>
-      <c r="H439">
+      <c r="H439" s="1">
         <v>19046</v>
       </c>
       <c r="I439" s="1" t="s">
@@ -14687,7 +14687,7 @@
       <c r="G440" t="s">
         <v>8</v>
       </c>
-      <c r="H440">
+      <c r="H440" s="1">
         <v>19046</v>
       </c>
       <c r="I440" s="1" t="s">
@@ -14716,7 +14716,7 @@
       <c r="G441" t="s">
         <v>8</v>
       </c>
-      <c r="H441">
+      <c r="H441" s="1">
         <v>19046</v>
       </c>
       <c r="I441" s="1" t="s">
@@ -14745,7 +14745,7 @@
       <c r="G442" t="s">
         <v>8</v>
       </c>
-      <c r="H442">
+      <c r="H442" s="1">
         <v>19046</v>
       </c>
       <c r="I442" s="1" t="s">
@@ -14774,7 +14774,7 @@
       <c r="G443" t="s">
         <v>8</v>
       </c>
-      <c r="H443">
+      <c r="H443" s="1">
         <v>19046</v>
       </c>
       <c r="I443" s="1" t="s">
@@ -14803,7 +14803,7 @@
       <c r="G444" t="s">
         <v>8</v>
       </c>
-      <c r="H444">
+      <c r="H444" s="1">
         <v>19046</v>
       </c>
       <c r="I444" s="1" t="s">
@@ -14832,7 +14832,7 @@
       <c r="G445" t="s">
         <v>8</v>
       </c>
-      <c r="H445">
+      <c r="H445" s="1">
         <v>19046</v>
       </c>
       <c r="I445" s="1" t="s">
@@ -14861,7 +14861,7 @@
       <c r="G446" t="s">
         <v>8</v>
       </c>
-      <c r="H446">
+      <c r="H446" s="1">
         <v>19046</v>
       </c>
       <c r="I446" s="1" t="s">
@@ -14890,7 +14890,7 @@
       <c r="G447" t="s">
         <v>8</v>
       </c>
-      <c r="H447">
+      <c r="H447" s="1">
         <v>19046</v>
       </c>
       <c r="I447" s="1" t="s">
@@ -14919,7 +14919,7 @@
       <c r="G448" t="s">
         <v>8</v>
       </c>
-      <c r="H448">
+      <c r="H448" s="1">
         <v>19046</v>
       </c>
       <c r="I448" s="1" t="s">
@@ -14948,7 +14948,7 @@
       <c r="G449" t="s">
         <v>8</v>
       </c>
-      <c r="H449">
+      <c r="H449" s="1">
         <v>19046</v>
       </c>
       <c r="I449" s="1" t="s">
@@ -14977,7 +14977,7 @@
       <c r="G450" t="s">
         <v>8</v>
       </c>
-      <c r="H450">
+      <c r="H450" s="1">
         <v>19046</v>
       </c>
       <c r="I450" s="1" t="s">
@@ -15006,7 +15006,7 @@
       <c r="G451" t="s">
         <v>8</v>
       </c>
-      <c r="H451">
+      <c r="H451" s="1">
         <v>19046</v>
       </c>
       <c r="I451" s="1" t="s">
@@ -15035,7 +15035,7 @@
       <c r="G452" t="s">
         <v>8</v>
       </c>
-      <c r="H452">
+      <c r="H452" s="1">
         <v>19046</v>
       </c>
       <c r="I452" s="1" t="s">
@@ -15064,7 +15064,7 @@
       <c r="G453" t="s">
         <v>8</v>
       </c>
-      <c r="H453">
+      <c r="H453" s="1">
         <v>19046</v>
       </c>
       <c r="I453" s="1" t="s">
@@ -15093,7 +15093,7 @@
       <c r="G454" t="s">
         <v>8</v>
       </c>
-      <c r="H454">
+      <c r="H454" s="1">
         <v>19046</v>
       </c>
       <c r="I454" s="1" t="s">
@@ -15122,7 +15122,7 @@
       <c r="G455" t="s">
         <v>8</v>
       </c>
-      <c r="H455">
+      <c r="H455" s="1">
         <v>19046</v>
       </c>
       <c r="I455" s="1" t="s">
@@ -15151,7 +15151,7 @@
       <c r="G456" t="s">
         <v>8</v>
       </c>
-      <c r="H456">
+      <c r="H456" s="1">
         <v>19046</v>
       </c>
       <c r="I456" s="1" t="s">
@@ -15180,7 +15180,7 @@
       <c r="G457" t="s">
         <v>8</v>
       </c>
-      <c r="H457">
+      <c r="H457" s="1">
         <v>19046</v>
       </c>
       <c r="I457" s="1" t="s">
@@ -15209,7 +15209,7 @@
       <c r="G458" t="s">
         <v>8</v>
       </c>
-      <c r="H458">
+      <c r="H458" s="1">
         <v>19046</v>
       </c>
       <c r="I458" s="1" t="s">
@@ -15238,7 +15238,7 @@
       <c r="G459" t="s">
         <v>8</v>
       </c>
-      <c r="H459">
+      <c r="H459" s="1">
         <v>19046</v>
       </c>
       <c r="I459" s="1" t="s">
@@ -15267,7 +15267,7 @@
       <c r="G460" t="s">
         <v>8</v>
       </c>
-      <c r="H460">
+      <c r="H460" s="1">
         <v>19046</v>
       </c>
       <c r="I460" s="1" t="s">
